--- a/workspaces/btc_daily_14days/on_chain/hash_rate_ma_ratio_90.xlsx
+++ b/workspaces/btc_daily_14days/on_chain/hash_rate_ma_ratio_90.xlsx
@@ -575,46 +575,46 @@
         <v>13</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-21.7242075509827</v>
+        <v>-21.6536863111931</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-23.34166413071678</v>
+        <v>-23.26518556267771</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-31.43877445693604</v>
+        <v>-31.33596464538485</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-31.31635260738131</v>
+        <v>-31.21387717311386</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-31.86325059251275</v>
+        <v>-31.75884451410553</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-31.57336898768769</v>
+        <v>-31.47018725945195</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-31.66618429792025</v>
+        <v>-31.5626894063122</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-24.43646674398004</v>
+        <v>-24.35628717765132</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-24.50377406090442</v>
+        <v>-24.42336736540741</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-9.942557271081569</v>
+        <v>-9.909689727652292</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-10.15037969015357</v>
+        <v>-10.11680907788717</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-10.1186934927532</v>
+        <v>-10.08498743802859</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-10.54301568822179</v>
+        <v>-10.50771192148907</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-2.577982242339552</v>
+        <v>-2.568398571263764</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>22</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2.052016225244564</v>
+        <v>2.045573944526346</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-4.106118383401935</v>
+        <v>-4.091734530429463</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-9.050051714303031</v>
+        <v>-9.019394275306475</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.1756849923276391</v>
+        <v>0.1763005248316745</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>8.736670717951903</v>
+        <v>8.709514355522622</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>9.036689369692454</v>
+        <v>9.008264823289693</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>8.954011616677128</v>
+        <v>8.925869905445218</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>8.488136290018524</v>
+        <v>8.461585546450138</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>8.429054285709583</v>
+        <v>8.402705827043548</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>12.13508905686575</v>
+        <v>12.09620483366368</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>16.4896876587004</v>
+        <v>16.436625262913</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>11.97001588093586</v>
+        <v>11.93194143617438</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>20.66959302134335</v>
+        <v>20.60335856483244</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>20.92519909811372</v>
+        <v>20.85817485529854</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>28</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-6.064866891640172</v>
+        <v>-6.04471732036594</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-7.67846395889886</v>
+        <v>-7.65215905305989</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.9291225833099332</v>
+        <v>-0.9247642360134734</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.7990819835243101</v>
+        <v>-0.7952554431028958</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2.236697565592948</v>
+        <v>2.230557844430948</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-1.040844543494032</v>
+        <v>-1.036512084447793</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2.450805980169314</v>
+        <v>2.443679078776164</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-1.594458870571522</v>
+        <v>-1.588212293635458</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-15.97073246945145</v>
+        <v>-15.91723264578651</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-13.24699090058695</v>
+        <v>-13.20295732088523</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-13.45562225129643</v>
+        <v>-13.41095059525785</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-20.58763877043789</v>
+        <v>-20.51920517974904</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-13.84992903067047</v>
+        <v>-13.8035643810488</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-17.18620647237965</v>
+        <v>-17.12883813170707</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>52</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>7.121946295175519</v>
+        <v>7.098597760473723</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-6.029731455996867</v>
+        <v>-6.008377659297359</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-12.1986459084841</v>
+        <v>-12.15667166184911</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-6.297831046422779</v>
+        <v>-6.275615709628575</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2.786750405763549</v>
+        <v>2.778653239770371</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.7658011564460097</v>
+        <v>-0.7622957894382907</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.8509042618003093</v>
+        <v>-0.8471827817809299</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-3.245840425224465</v>
+        <v>-3.233966879445305</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2.472980780517375</v>
+        <v>2.466160858699375</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1.621826746036696</v>
+        <v>1.617250709182962</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.5110813720471796</v>
+        <v>-0.5085985733180465</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>1.451294025484025</v>
+        <v>1.447742104108904</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>1.030096577098703</v>
+        <v>1.027862056398561</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.6487973527751976</v>
+        <v>-0.6453216481947095</v>
       </c>
     </row>
     <row r="10">
@@ -780,49 +780,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1.077990251218594</v>
+        <v>1.114147433892086</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>17.32794087474561</v>
+        <v>17.90238838939158</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1.841061396256052</v>
+        <v>1.884218389396182</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1.967442103353598</v>
+        <v>2.018720424713912</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-2.137989132930528</v>
+        <v>-2.221831746031356</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-7.209279422943681</v>
+        <v>-7.465170573491598</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>4.415274746272324</v>
+        <v>4.55612051705171</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.395890226318549</v>
+        <v>-1.455969000793679</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.454227367275116</v>
+        <v>-1.517324707995293</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.492714109752157</v>
+        <v>-0.5173150804319988</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.690243544541616</v>
+        <v>-0.7220910373264928</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-4.232841446851012</v>
+        <v>-4.389686128104167</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-4.641016304142433</v>
+        <v>-4.811076786687316</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-6.189721140993143</v>
+        <v>-6.414552417424602</v>
       </c>
     </row>
     <row r="11">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-10.6329732039309</v>
+        <v>-10.7294827172453</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-7.59546230854825</v>
+        <v>-7.666417313053692</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-9.153624406404738</v>
+        <v>-9.241741961302985</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-7.862413730240618</v>
+        <v>-7.937765526802004</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-8.403408007651016</v>
+        <v>-8.482924997146043</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-10.43609275308641</v>
+        <v>-10.53452586345413</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-9.356687343764818</v>
+        <v>-9.443611216704213</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-9.827270293009406</v>
+        <v>-9.920022321821165</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-9.891139073840833</v>
+        <v>-9.984757004266719</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-14.24012685535622</v>
+        <v>-14.37153624286557</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-6.796919596032048</v>
+        <v>-6.860945424870792</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-9.093572768382224</v>
+        <v>-9.180069022276498</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-7.181453713693095</v>
+        <v>-7.250463943955467</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-8.101155850300167</v>
+        <v>-8.179258299777011</v>
       </c>
     </row>
     <row r="12">
@@ -884,49 +884,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-5.338966775494526</v>
+        <v>-5.370810450896911</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.366523096897474</v>
+        <v>0.3663220856607978</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.8417891657434211</v>
+        <v>-0.8510270502462873</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.728537021361575</v>
+        <v>1.734800119641662</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.25100416896808</v>
+        <v>-1.261326095947524</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-2.581647658385556</v>
+        <v>-2.600125027322974</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-4.294040515341813</v>
+        <v>-4.321042005078681</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.1213346127313741</v>
+        <v>0.1184525648798243</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.06003918888436743</v>
+        <v>0.05661521271388636</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.420867221810198</v>
+        <v>-2.437929567493221</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>3.076302157986532</v>
+        <v>3.091455490589141</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.296173559425625</v>
+        <v>2.305531925670167</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.2454268711772016</v>
+        <v>0.2434241357066398</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-4.744149429055376</v>
+        <v>-4.775208155129896</v>
       </c>
     </row>
     <row r="13">
@@ -936,49 +936,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-2.186689853952309</v>
+        <v>-2.196795088381364</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.572125495147063</v>
+        <v>-2.583600804792951</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.739884548238464</v>
+        <v>-1.749807434636914</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-4.679409726997314</v>
+        <v>-4.699747112082761</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-7.675944828432122</v>
+        <v>-7.707943438008265</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-4.309701081376744</v>
+        <v>-4.329285157743868</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-5.008543443127159</v>
+        <v>-5.030177887368261</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-6.092458898132108</v>
+        <v>-6.118441377838522</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-7.999242601389483</v>
+        <v>-8.032722279351361</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.741953111394608</v>
+        <v>-1.751263849417107</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.947314430028491</v>
+        <v>-1.956096519670474</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.297878514954647</v>
+        <v>-1.305198219010308</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-4.791593179161922</v>
+        <v>-4.8124218978489</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-2.697029546890221</v>
+        <v>-2.710848713720893</v>
       </c>
     </row>
     <row r="14">
@@ -988,49 +988,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-2.983634398641343</v>
+        <v>-3.030975641411715</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.6740111693778559</v>
+        <v>-0.6902809346715557</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.4019116099583329</v>
+        <v>0.3945363353071443</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-4.863310025038352</v>
+        <v>-4.939595401525374</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.248553936491447</v>
+        <v>1.25175749240065</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2.035515607242566</v>
+        <v>2.049288118254545</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.9933234996470262</v>
+        <v>-1.018156355717061</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.994980858402819</v>
+        <v>0.9954536419373312</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.752133390732169</v>
+        <v>-0.7767403528939099</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>2.819610602600598</v>
+        <v>2.846820515249519</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.632027100578568</v>
+        <v>1.648019355968849</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.2952009311434267</v>
+        <v>-0.3083615948239355</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.882849480424589</v>
+        <v>-2.932930466119025</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.6701040666256333</v>
+        <v>-0.6931593825987292</v>
       </c>
     </row>
     <row r="15">
@@ -1040,49 +1040,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.273174003029354</v>
+        <v>-2.282644992610109</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.682860166497015</v>
+        <v>-1.690006089399688</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-4.281346728026243</v>
+        <v>-4.297709013059034</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.584235747327448</v>
+        <v>-2.595975032570131</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.9179183112644509</v>
+        <v>-0.9238557481327376</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.06323564195435</v>
+        <v>-1.069461177172983</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-2.029146729040576</v>
+        <v>-2.0384885912313</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-4.259646469108191</v>
+        <v>-4.275847242612151</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-5.201524953284284</v>
+        <v>-5.22141137761983</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-5.168676413321158</v>
+        <v>-5.186771132000011</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-8.901448652657976</v>
+        <v>-8.930213992536196</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-4.457934727358762</v>
+        <v>-4.474107634331205</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-5.316928490134387</v>
+        <v>-5.336840121382203</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.980019095381849</v>
+        <v>-1.989773656362559</v>
       </c>
     </row>
     <row r="16">
@@ -1092,49 +1092,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.822385688631023</v>
+        <v>-2.830812474898011</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-3.266541949081393</v>
+        <v>-3.275475073238631</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.355537151286264</v>
+        <v>-1.361562613378041</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2.064081601350495</v>
+        <v>2.065372414825951</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>3.171045613472231</v>
+        <v>3.175525859506543</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.822889210710059</v>
+        <v>1.824500989098489</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.2356721661714971</v>
+        <v>-0.2388414254493441</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.031005684224169</v>
+        <v>-1.036241164650541</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.103432353954112</v>
+        <v>-0.1073595004762993</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.3638663992895346</v>
+        <v>0.3622613667131702</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.157216127344491</v>
+        <v>-1.162081985569436</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.4649106813534871</v>
+        <v>-0.4684415810002136</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.8832865656052675</v>
+        <v>-0.8886961919451153</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.622427975246097</v>
+        <v>-1.629073869569886</v>
       </c>
     </row>
     <row r="17">
@@ -1144,49 +1144,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.798993875765532</v>
+        <v>-1.820238749644368</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.06165473349251016</v>
+        <v>0.05389991258530813</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.402897138006956</v>
+        <v>1.40104682106147</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.591849729385622</v>
+        <v>-1.611628691957456</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.43582650001327</v>
+        <v>-1.451274436801043</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.7918968398763013</v>
+        <v>-0.8037567002974626</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-2.613628318877659</v>
+        <v>-2.63980479662137</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.452348874336117</v>
+        <v>-0.4659244066027881</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-2.943888185508058</v>
+        <v>-2.975625646196164</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-3.098837983966419</v>
+        <v>-3.126960756749426</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-3.649947753393171</v>
+        <v>-3.682513336576072</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-3.415668565562527</v>
+        <v>-3.446816341553188</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.050802689965515</v>
+        <v>-1.069868155295218</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.5859855596535439</v>
+        <v>0.5784545755824624</v>
       </c>
     </row>
     <row r="18">
@@ -1196,49 +1196,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.657317918872181</v>
+        <v>-1.66894454871526</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.931098889696131</v>
+        <v>-1.942203483310202</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-3.32931207789791</v>
+        <v>-3.346245999814798</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.8143189811309881</v>
+        <v>0.8111263704335343</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.061894876081723</v>
+        <v>-1.069439923804957</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.760068713469721</v>
+        <v>0.7585207322586953</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.680998245636765</v>
+        <v>1.680498424382385</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3.556588747895674</v>
+        <v>3.56230831419149</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>4.835563873580092</v>
+        <v>4.843590307203819</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>2.982367003162544</v>
+        <v>2.986753712779922</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.7722886967131259</v>
+        <v>0.7685775696703914</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.8065354559506162</v>
+        <v>0.8029607270157513</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.726528653088096</v>
+        <v>1.724987995265479</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.9709959302486553</v>
+        <v>0.9679979181457909</v>
       </c>
     </row>
     <row r="19">
@@ -2213,10 +2213,8 @@
           <t>X &gt; -0.0127</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4006~4019</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4006</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>0.007183725074916936</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; -0.01139</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>3993~4006</t>
-        </is>
+      <c r="B7" t="n">
+        <v>3993</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>0.07770496486241285</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; -0.01007</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3971~3984</t>
-        </is>
+      <c r="B8" t="n">
+        <v>3971</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>0.06680264364544541</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; -0.00875</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3943~3956</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3943</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>0.1102017202349259</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; -0.007432</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3891~3904</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3891</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>0.01680758142936867</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; -0.006114</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3837~3848</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3837</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>0.001364174592517031</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; -0.004796</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3752~3762</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3752</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>0.2444670492743413</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; -0.003478</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3630~3639</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3630</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>0.4331898743489688</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; -0.00216</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3468~3476</t>
-        </is>
+      <c r="B14" t="n">
+        <v>3468</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>0.5560438431962353</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; -0.0008421</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3267~3272</t>
-        </is>
+      <c r="B15" t="n">
+        <v>3267</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>0.7767328289342785</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; 0.000476</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>3041~3045</t>
-        </is>
+      <c r="B16" t="n">
+        <v>3041</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>1.004098625602829</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; 0.001794</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2738~2741</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2738</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>1.428487984058542</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; 0.003112</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2452~2453</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2452</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>1.807417774368091</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; 0.00443</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2154~2154</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2154</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>2.288362979697176</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; 0.005748</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1849~1849</t>
-        </is>
+      <c r="B20" t="n">
+        <v>1849</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>1.91434967330003</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 0.007066</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1528~1528</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1528</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>1.825933407538713</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 0.008384</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1234~1234</t>
-        </is>
+      <c r="B22" t="n">
+        <v>1234</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>1.882574645754374</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 0.009702</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1037~1037</t>
-        </is>
+      <c r="B23" t="n">
+        <v>1037</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>1.701354350956848</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 0.01102</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>844~844</t>
-        </is>
+      <c r="B24" t="n">
+        <v>844</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>1.534997698747375</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 0.01234</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>697~697</t>
-        </is>
+      <c r="B25" t="n">
+        <v>697</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>3.604122655399784</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 0.01366</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>582~582</t>
-        </is>
+      <c r="B26" t="n">
+        <v>582</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>4.379413913466998</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 0.01497</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>471~471</t>
-        </is>
+      <c r="B27" t="n">
+        <v>471</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>4.619088219068153</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 0.01629</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>372~372</t>
-        </is>
+      <c r="B28" t="n">
+        <v>372</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>3.151722970112601</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 0.01761</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>301~301</t>
-        </is>
+      <c r="B29" t="n">
+        <v>301</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>1.991611513677071</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 0.01893</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>246~246</t>
-        </is>
+      <c r="B30" t="n">
+        <v>246</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>2.791114525318484</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 0.02025</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>198~198</t>
-        </is>
+      <c r="B31" t="n">
+        <v>198</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>2.557066730295077</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 0.02156</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>164~164</t>
-        </is>
+      <c r="B32" t="n">
+        <v>164</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>3.604122655399784</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 0.02288</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>133~133</t>
-        </is>
+      <c r="B33" t="n">
+        <v>133</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>1.641900025654685</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 0.0242</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>109~109</t>
-        </is>
+      <c r="B34" t="n">
+        <v>109</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-1.117291531219145</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 0.02552</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>83~83</t>
-        </is>
+      <c r="B35" t="n">
+        <v>83</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>1.723429149669542</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; -0.0127</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>83~83</t>
-        </is>
+      <c r="B6" t="n">
+        <v>83</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>1.723429149669542</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; -0.01139</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>96~96</t>
-        </is>
+      <c r="B7" t="n">
+        <v>96</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-1.451771653543311</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; -0.01007</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>118~118</t>
-        </is>
+      <c r="B8" t="n">
+        <v>118</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.7985230659726881</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; -0.00875</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>146~146</t>
-        </is>
+      <c r="B9" t="n">
+        <v>146</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-1.808506813360658</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; -0.007432</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>198~198</t>
-        </is>
+      <c r="B10" t="n">
+        <v>198</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>0.5368647100930559</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; -0.006114</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>252~254</t>
-        </is>
+      <c r="B11" t="n">
+        <v>252</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>0.6561679790026318</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; -0.004796</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>337~340</t>
-        </is>
+      <c r="B12" t="n">
+        <v>337</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-2.199320673151149</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; -0.003478</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>459~463</t>
-        </is>
+      <c r="B13" t="n">
+        <v>459</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-3.033395123665699</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; -0.00216</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>621~626</t>
-        </is>
+      <c r="B14" t="n">
+        <v>621</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-2.812927138101351</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; -0.0008421</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>822~830</t>
-        </is>
+      <c r="B15" t="n">
+        <v>822</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-2.854884103342506</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; 0.000476</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1048~1057</t>
-        </is>
+      <c r="B16" t="n">
+        <v>1048</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-2.729956768648954</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; 0.001794</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1351~1361</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1351</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-2.750602170320192</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; 0.003112</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1637~1649</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1637</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-2.584402540949817</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; 0.00443</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1935~1948</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1935</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-2.442103617951247</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; 0.005748</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2240~2253</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2240</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-1.494769878132743</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 0.007066</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2561~2574</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2561</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-1.017136843908496</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 0.008384</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2855~2868</t>
-        </is>
+      <c r="B22" t="n">
+        <v>2855</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.7500631458724598</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 0.009702</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>3052~3065</t>
-        </is>
+      <c r="B23" t="n">
+        <v>3052</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.5195394621349365</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 0.01102</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>3245~3258</t>
-        </is>
+      <c r="B24" t="n">
+        <v>3245</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-0.3448809230337986</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 0.01234</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3392~3405</t>
-        </is>
+      <c r="B25" t="n">
+        <v>3392</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-0.6872709193289239</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 0.01366</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3507~3520</t>
-        </is>
+      <c r="B26" t="n">
+        <v>3507</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-0.6752565020281551</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 0.01497</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3618~3631</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3618</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-0.5518244397362722</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 0.01629</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3717~3730</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3717</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-0.2682372478239117</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 0.01761</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3788~3801</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3788</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-0.1124859392575885</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 0.01893</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3843~3856</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3843</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-0.1334798139859075</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 0.02025</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3891~3904</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3891</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-0.08565143496407757</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 0.02156</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>3925~3938</t>
-        </is>
+      <c r="B32" t="n">
+        <v>3925</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-0.1064398438260241</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 0.02288</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>3956~3969</t>
-        </is>
+      <c r="B33" t="n">
+        <v>3956</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-0.01170488609558618</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 0.0242</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>3980~3993</t>
-        </is>
+      <c r="B34" t="n">
+        <v>3980</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>0.07355391620374974</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 0.02552</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4006~4019</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4006</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>0.007183725074916936</v>

--- a/workspaces/btc_daily_14days/on_chain/hash_rate_ma_ratio_90.xlsx
+++ b/workspaces/btc_daily_14days/on_chain/hash_rate_ma_ratio_90.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Hash Rate MA Ratio-90 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Hash Rate MA Ratio-90 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -568,53 +568,53 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.01205</t>
+          <t>X ≈ -0.01204</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>13</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-21.6536863111931</v>
+        <v>-21.64122399141183</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-23.26518556267771</v>
+        <v>-23.25233387006845</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-31.33596464538485</v>
+        <v>-31.32301665503208</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-31.21387717311386</v>
+        <v>-31.20095168404661</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-31.75884451410553</v>
+        <v>-31.74578267963633</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-31.47018725945195</v>
+        <v>-31.457187529805</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-31.5626894063122</v>
+        <v>-31.54966101890409</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-24.35628717765132</v>
+        <v>-24.34313614014182</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-24.42336736540741</v>
+        <v>-24.41019365519065</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-9.909689727652292</v>
+        <v>-9.89630116281797</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-10.11680907788717</v>
+        <v>-10.10336429259401</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-10.08498743802859</v>
+        <v>-10.07154350218827</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-10.50771192148907</v>
+        <v>-10.4941601147645</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-2.568398571263764</v>
+        <v>-2.57882820697241</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>22</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2.045573944526346</v>
+        <v>2.058055050899021</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-4.091734530429463</v>
+        <v>-4.078868961292564</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-9.019394275306475</v>
+        <v>-9.006431476499117</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.1763005248316745</v>
+        <v>0.1892452192997638</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>8.709514355522622</v>
+        <v>8.722598638569046</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>9.008264823289693</v>
+        <v>9.021284522198222</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>8.925869905445218</v>
+        <v>8.938915773610056</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>8.461585546450138</v>
+        <v>8.474748703402028</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>8.402705827043548</v>
+        <v>8.415889641287407</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>12.09620483366368</v>
+        <v>12.10959880538215</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>16.436625262913</v>
+        <v>16.4500749675617</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>11.93194143617438</v>
+        <v>11.94538807730445</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>20.60335856483244</v>
+        <v>20.6169123001456</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>20.85817485529854</v>
+        <v>20.84774521960659</v>
       </c>
     </row>
     <row r="8">
@@ -679,462 +679,462 @@
         <v>28</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-6.04471732036594</v>
+        <v>-6.032243454580538</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-7.65215905305989</v>
+        <v>-7.639296824691485</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.9247642360134734</v>
+        <v>-0.9117963711022483</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.7952554431028958</v>
+        <v>-0.7823118089318442</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2.230557844430948</v>
+        <v>2.24363811127234</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-1.036512084447793</v>
+        <v>-1.023497779777571</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2.443679078776164</v>
+        <v>2.456721824948062</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-1.588212293635458</v>
+        <v>-1.575053194874762</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-15.91723264578651</v>
+        <v>-15.90405679738743</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-13.20295732088523</v>
+        <v>-13.18956995276004</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-13.41095059525785</v>
+        <v>-13.39750670096092</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-20.51920517974904</v>
+        <v>-20.50576276270716</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-13.8035643810488</v>
+        <v>-13.79001287058927</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-17.12883813170707</v>
+        <v>-17.13926776740847</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.008091</t>
+          <t>X ≈ -0.00809</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>52</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>7.098597760473723</v>
+        <v>7.111081773297435</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-6.008377659297359</v>
+        <v>-5.99551523529253</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-12.15667166184911</v>
+        <v>-12.14371275675274</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-6.275615709628575</v>
+        <v>-6.262676428577016</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2.778653239770371</v>
+        <v>2.791733227748573</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.7622957894382907</v>
+        <v>-0.7492819407527449</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.8471827817809299</v>
+        <v>-0.8341420161403121</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-3.233966879445305</v>
+        <v>-3.2208088966145</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2.466160858699375</v>
+        <v>2.479342190458119</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1.617250709182962</v>
+        <v>1.630641551656119</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.5085985733180465</v>
+        <v>-0.4951524546488102</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>1.447742104108904</v>
+        <v>1.461187162386366</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>1.027862056398561</v>
+        <v>1.041414433935991</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.6453216481947095</v>
+        <v>-0.6557512838919806</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.006773</t>
+          <t>X ≈ -0.006772</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1.114147433892086</v>
+        <v>0.1551647105392675</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>17.90238838939158</v>
+        <v>18.42257825327714</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1.884218389396182</v>
+        <v>1.690135671099419</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>2.018720424713912</v>
+        <v>2.822938944535814</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-2.221831746031356</v>
+        <v>-1.349936513405204</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-7.465170573491598</v>
+        <v>-6.492398571405772</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>4.55612051705171</v>
+        <v>4.312097677392238</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.455969000793679</v>
+        <v>-0.6023736003043183</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.517324707995293</v>
+        <v>-0.6634891611974183</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.5173150804319988</v>
+        <v>0.3033142739067856</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.7220910373264928</v>
+        <v>0.09880441410968643</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-4.389686128104167</v>
+        <v>-3.501276605414084</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-4.811076786687316</v>
+        <v>-3.922331773783348</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-6.414552417424602</v>
+        <v>-5.515891144031848</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.005455</t>
+          <t>X ≈ -0.005454</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-10.7294827172453</v>
+        <v>-10.22143891522423</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-7.666417313053692</v>
+        <v>-8.289601093510548</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-9.241741961302985</v>
+        <v>-9.881814018246551</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-7.937765526802004</v>
+        <v>-8.561109227515288</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-8.482924997146043</v>
+        <v>-9.106362724481954</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-10.53452586345413</v>
+        <v>-11.18612624565807</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-9.443611216704213</v>
+        <v>-10.08407877472225</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-9.920022321821165</v>
+        <v>-10.55774128438527</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-9.984757004266719</v>
+        <v>-10.62263673097291</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-14.37153624286557</v>
+        <v>-15.05145243562016</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-6.860945424870792</v>
+        <v>-8.12370425592588</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-9.180069022276498</v>
+        <v>-9.796548386803124</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-7.250463943955467</v>
+        <v>-7.838995852950291</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-8.179258299777011</v>
+        <v>-8.805934434075141</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.004137</t>
+          <t>X ≈ -0.004136</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-5.370810450896911</v>
+        <v>-5.311143884257937</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.3663220856607978</v>
+        <v>0.3794939025303989</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.8510270502462873</v>
+        <v>-0.8247760322783222</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.734800119641662</v>
+        <v>1.738466904971496</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.261326095947524</v>
+        <v>-1.232949273786865</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-2.600125027322974</v>
+        <v>-2.559727496017814</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-4.321042005078681</v>
+        <v>-4.2692650842123</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.1184525648798243</v>
+        <v>0.135883675311824</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.05661521271388636</v>
+        <v>0.07487115667544231</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.437929567493221</v>
+        <v>-2.399254033012831</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>3.091455490589141</v>
+        <v>3.083188219785967</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.305531925670167</v>
+        <v>2.305108586905128</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.2434241357066398</v>
+        <v>0.2599436732264166</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-4.775208155129896</v>
+        <v>-4.392461727919496</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.002819</t>
+          <t>X ≈ -0.002818</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>162</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-2.196795088381364</v>
+        <v>-2.18346451795486</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.583600804792951</v>
+        <v>-2.569774025252698</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.749807434636914</v>
+        <v>-1.736800303219312</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-4.699747112082761</v>
+        <v>-4.685182165908046</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-7.707943438008265</v>
+        <v>-7.692367699617556</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-4.329285157743868</v>
+        <v>-4.314702716674603</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-5.030177887368261</v>
+        <v>-5.017111633067785</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-6.118441377838522</v>
+        <v>-6.10323576068788</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-8.032722279351361</v>
+        <v>-8.016931612093551</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.751263849417107</v>
+        <v>-2.087850920862891</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.956096519670474</v>
+        <v>-1.942639225960257</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.305198219010308</v>
+        <v>-1.291205952747411</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-4.8124218978489</v>
+        <v>-4.797307736145598</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-2.710848713720893</v>
+        <v>-2.721278349419045</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.001501</t>
+          <t>X ≈ -0.0015</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>201</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-3.030975641411715</v>
+        <v>-3.017158075840435</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.6902809346715557</v>
+        <v>-0.6767841028042909</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.3945363353071443</v>
+        <v>0.4075434667247464</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-4.939595401525374</v>
+        <v>-4.924631771949265</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.25175749240065</v>
+        <v>0.987154369825582</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2.049288118254545</v>
+        <v>2.062156395227909</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.018156355717061</v>
+        <v>-1.005090101416585</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.9954536419373312</v>
+        <v>1.008774543140447</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.7767403528939099</v>
+        <v>-1.043454893295085</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>2.846820515249519</v>
+        <v>2.86022564290235</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.648019355968849</v>
+        <v>1.661476649679066</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.3083615948239355</v>
+        <v>-0.2945275905328089</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.932930466119025</v>
+        <v>-3.205490681927259</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.6931593825987292</v>
+        <v>-0.7035890182968814</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.0001831</t>
+          <t>X ≈ -0.0001822</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.282644992610109</v>
+        <v>-2.489883820504254</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.690006089399688</v>
+        <v>-1.466925527662504</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-4.297709013059034</v>
+        <v>-4.505614132041607</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.595975032570131</v>
+        <v>-2.615220474649362</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.9238557481327376</v>
+        <v>-0.7082230370289508</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.069461177172983</v>
+        <v>-0.8513051250043233</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-2.0384885912313</v>
+        <v>-1.816989943947597</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-4.275847242612151</v>
+        <v>-4.044733033093884</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-5.22141137761983</v>
+        <v>-4.988020058382908</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-5.186771132000011</v>
+        <v>-4.957070688165956</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-8.930213992536196</v>
+        <v>-8.684872203851455</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-4.474107634331205</v>
+        <v>-4.246545652322055</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-5.336840121382203</v>
+        <v>-5.108867483084872</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.989773656362559</v>
+        <v>-1.799431392329801</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ 0.001135</t>
+          <t>X ≈ 0.001136</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.830812474898011</v>
+        <v>-2.65269960747478</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-3.275475073238631</v>
+        <v>-3.606717357237471</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.361562613378041</v>
+        <v>-1.172783206329576</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2.065372414825951</v>
+        <v>1.934240724257997</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>3.175525859506543</v>
+        <v>3.049984043948342</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.824500989098489</v>
+        <v>1.693145363291379</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.2388414254493441</v>
+        <v>-0.3764854560541977</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.036241164650541</v>
+        <v>-1.174006320499132</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.1073595004762993</v>
+        <v>-0.2427358073722203</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.3622613667131702</v>
+        <v>0.231461182199034</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.162081985569436</v>
+        <v>-1.29719968640309</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.4684415810002136</v>
+        <v>-0.6007996585337807</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.8886961919451153</v>
+        <v>-1.021578630501608</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.629073869569886</v>
+        <v>-1.789220463718777</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>286</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.820238749644368</v>
+        <v>-1.806271230815227</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.05389991258530813</v>
+        <v>0.06680972216135928</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.40104682106147</v>
+        <v>1.414053952479073</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.611628691957456</v>
+        <v>-1.598649549558992</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.451274436801043</v>
+        <v>-1.438163632426104</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.8037567002974626</v>
+        <v>-0.7898408972748072</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-2.63980479662137</v>
+        <v>-2.626738542320894</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.4659244066027881</v>
+        <v>-0.6511039039882576</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-2.975625646196164</v>
+        <v>-2.962426907241401</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-3.126960756749426</v>
+        <v>-3.113555629096595</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-3.682513336576072</v>
+        <v>-3.669056042865854</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-3.446816341553188</v>
+        <v>-3.634550234304122</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.069868155295218</v>
+        <v>-1.056312108943615</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.5784545755824624</v>
+        <v>0.5680249398843102</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>298</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.66894454871526</v>
+        <v>-1.654745146985036</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.942203483310202</v>
+        <v>-1.929293673734151</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-3.346245999814798</v>
+        <v>-3.333238868397196</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.8111263704335343</v>
+        <v>0.8241055128319985</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.069439923804957</v>
+        <v>-1.056329119430018</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.7585207322586953</v>
+        <v>0.5842843895989773</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.680498424382385</v>
+        <v>1.693564678682861</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3.56230831419149</v>
+        <v>3.575489323486728</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>4.843590307203819</v>
+        <v>4.856789046158582</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>2.986753712779922</v>
+        <v>3.000158840432753</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.7685775696703914</v>
+        <v>0.7820348633806091</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.8029607270157513</v>
+        <v>0.8164130157358613</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.724987995265479</v>
+        <v>1.738544041617082</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.9679979181457909</v>
+        <v>0.9575682824476388</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>305</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>4.555742007658878</v>
+        <v>4.388735180906842</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>2.288430689776661</v>
+        <v>2.301340499352712</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.07365113157410264</v>
+        <v>-0.06064400015650051</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.040208558410448</v>
+        <v>1.053187700808913</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.813262753174413</v>
+        <v>1.826373557549353</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.4713604285949913</v>
+        <v>0.4844033248893567</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.698102121158783</v>
+        <v>1.711168375459259</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>4.509607246967455</v>
+        <v>4.522788256262693</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2.481394246030902</v>
+        <v>2.494592984985665</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>3.92635102821616</v>
+        <v>3.939756155868992</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>6.016679671111767</v>
+        <v>6.030136964821985</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>6.70680053337523</v>
+        <v>6.72025282209534</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>5.302939365053135</v>
+        <v>5.316495411404738</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>6.208398402247603</v>
+        <v>6.197968766549451</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>321</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.335222115927088</v>
+        <v>2.347744405602711</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>5.708072178975293</v>
+        <v>5.720981988551344</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.9518327558678052</v>
+        <v>0.9648398872854074</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.7870729900293298</v>
+        <v>-0.7740938476308656</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.478244112655517</v>
+        <v>1.491354917030456</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>2.087212530121839</v>
+        <v>2.100255426416204</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3.871637691354202</v>
+        <v>3.884703945654678</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.22376893431732</v>
+        <v>1.236949943612558</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>3.654980886141388</v>
+        <v>3.668179625096151</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.9356968226086764</v>
+        <v>0.9491019502615075</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.977049417294147</v>
+        <v>1.990506711004365</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>3.569064973393587</v>
+        <v>3.582517262113697</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.9027044434456</v>
+        <v>1.916260489797203</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>4.333111133977198</v>
+        <v>4.322681498279046</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>294</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.588194332851209</v>
+        <v>1.600716622526832</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>3.037845209682906</v>
+        <v>3.050755019258958</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.962704394242778</v>
+        <v>1.97571152566038</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2.092957526850199</v>
+        <v>2.105936669248663</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.166552123596077</v>
+        <v>-1.153441319221137</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-3.250062566832753</v>
+        <v>-3.237019670538388</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.2735717943090776</v>
+        <v>-0.2605055400086016</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>2.320469296705262</v>
+        <v>2.3336503060005</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>3.620013628210039</v>
+        <v>3.633212367164802</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.069208171073299</v>
+        <v>1.08261329872613</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>4.605951445395178</v>
+        <v>4.619408739105396</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>6.341014874849414</v>
+        <v>6.354467163569524</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>4.560216046217477</v>
+        <v>4.573772092569079</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>3.109257106384923</v>
+        <v>3.098827470686771</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>197</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.836510918368816</v>
+        <v>2.849033208044439</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.820747973783369</v>
+        <v>-1.807838164207318</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>3.87575387799567</v>
+        <v>3.888761009413273</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.46793594461338</v>
+        <v>1.480915087011844</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.929514729541161</v>
+        <v>0.9426255339161003</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.7193424540587898</v>
+        <v>0.7323853503531552</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.8882339028072792</v>
+        <v>-0.8751676485068032</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.1674253380050672</v>
+        <v>0.180606347300305</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>4.167339157406467</v>
+        <v>4.18053789636123</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>3.317213972378653</v>
+        <v>3.330619100031484</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>4.12768907445696</v>
+        <v>4.141146368167178</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.131615379010455</v>
+        <v>2.145067667730565</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>4.757046047253418</v>
+        <v>4.770602093605021</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.976310526737777</v>
+        <v>2.965880891039625</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>193</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.428841472536043</v>
+        <v>2.441363762211665</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2.889806719675512</v>
+        <v>2.902716529251563</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>7.158150448312078</v>
+        <v>7.17115757972968</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>5.215864720815951</v>
+        <v>5.228843863214415</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.5323657855365269</v>
+        <v>0.5454765899114662</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.902346583355879</v>
+        <v>2.915389479650244</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.781343436031669</v>
+        <v>1.794409690332145</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.7960253222243523</v>
+        <v>0.8092063315195901</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.373782854113372</v>
+        <v>-2.360584115158609</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.439304396091742</v>
+        <v>1.452709523744574</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.39239193340709</v>
+        <v>-2.378934639696872</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-3.394278206113448</v>
+        <v>-3.380825917393338</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-3.814532817058407</v>
+        <v>-3.800976770706804</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-3.046676769756118</v>
+        <v>-3.05710640545427</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>147</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-8.275751245380008</v>
+        <v>-8.263228955704385</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-7.166236422970151</v>
+        <v>-7.1533266133941</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-5.520288803036131</v>
+        <v>-5.507281671618529</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-4.029491452741553</v>
+        <v>-4.016512310343089</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-3.207368450126644</v>
+        <v>-3.194257645751705</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.851978249493811</v>
+        <v>1.865021145788177</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.447516641065029</v>
+        <v>2.460582895365505</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.660605351127032</v>
+        <v>2.67378636042227</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.1214829704293905</v>
+        <v>-0.1082842314746273</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.3889360622297318</v>
+        <v>0.4023411898825628</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-3.217177806305543</v>
+        <v>-3.203720512595325</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.50252254011653</v>
+        <v>-2.48907025139642</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>2.519399719686866</v>
+        <v>2.532955766038469</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1.408576834276076</v>
+        <v>1.398147198577924</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>115</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.3195252767317172</v>
+        <v>-0.3070029870560944</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-5.409359759261186</v>
+        <v>-5.396449949685135</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-3.195532813683862</v>
+        <v>-3.18252568226626</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.326149246293753</v>
+        <v>-1.313170103895288</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.9950052439746244</v>
+        <v>-0.9818944395996851</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-5.914954610606834</v>
+        <v>-5.901911714312469</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.651862240922597</v>
+        <v>-1.638795986622121</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.3799152049214385</v>
+        <v>-0.3667341956262007</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.037345778461479</v>
+        <v>3.050544517416242</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.291040276131618</v>
+        <v>-1.277635148478787</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.2433368343333626</v>
+        <v>0.2567941280435804</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-3.200540877886418</v>
+        <v>-3.187088589166308</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.751230271440022</v>
+        <v>-2.737674225088419</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-3.371074156555089</v>
+        <v>-3.381503792253241</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>111</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.362417535645875</v>
+        <v>3.374939825321498</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.05095787912017613</v>
+        <v>-0.03804806954412498</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>7.662281522391339</v>
+        <v>7.675288653808941</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>9.59433645680064</v>
+        <v>9.607315599199104</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>11.75861794443117</v>
+        <v>11.7717287488061</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>9.353357179444131</v>
+        <v>9.366400075738497</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>4.764118957667399</v>
+        <v>4.777185211967875</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.910271648321363</v>
+        <v>-2.897090639026125</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.0703706336027</v>
+        <v>-2.057171894647936</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>3.38581048767562</v>
+        <v>3.399215615328451</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>4.982858965159835</v>
+        <v>4.996316258870053</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>2.314539419802571</v>
+        <v>2.327991708522681</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>5.497888412461329</v>
+        <v>5.511444458812932</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2.144006141133957</v>
+        <v>2.133576505435805</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>99</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>10.13282430605265</v>
+        <v>10.14534659572828</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>12.56165473349242</v>
+        <v>12.57456454306848</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>11.15668501679484</v>
+        <v>11.16969214821244</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>6.236433098897287</v>
+        <v>6.249412241295751</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>6.708112893926099</v>
+        <v>6.721223698301038</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>8.015655841742763</v>
+        <v>8.028698738037129</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>6.920821114369481</v>
+        <v>6.933887368669957</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.40313266508295</v>
+        <v>1.416313674378188</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>8.4128398496077</v>
+        <v>8.426038588562463</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>6.55261365447879</v>
+        <v>6.566018782131621</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>9.378163360464242</v>
+        <v>9.39162065417446</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>9.412546517809702</v>
+        <v>9.425998806529812</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>6.972089886662722</v>
+        <v>6.985645933014325</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>8.231912229040049</v>
+        <v>8.221482593341896</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>71</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>8.069941961480161</v>
+        <v>8.082464251155784</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.5838851726108132</v>
+        <v>-0.570975363034762</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.838147529243265</v>
+        <v>1.851154660660868</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.968400661850765</v>
+        <v>1.981379804249229</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.0215287425532793</v>
+        <v>0.03463954692821858</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>3.135872088719651</v>
+        <v>3.148914985014017</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>4.459589075672724</v>
+        <v>4.4726553299732</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>9.626208493792596</v>
+        <v>9.639389503087834</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>5.339856494934189</v>
+        <v>5.353055233888952</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.144071506995104</v>
+        <v>-1.130666379342273</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.348824831312683</v>
+        <v>-1.335367537602465</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.09400903025802165</v>
+        <v>0.1074613189781317</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>3.899106531989212</v>
+        <v>3.912662578340814</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>2.74037716004014</v>
+        <v>2.729947524341988</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>55</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-1.584347411119118</v>
+        <v>-1.571825121443496</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.4404426122803073</v>
+        <v>0.4533524218563585</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.500119360229235</v>
+        <v>5.513126491646837</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.994008856473037</v>
+        <v>2.006987998871502</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>6.910133095946378</v>
+        <v>6.923243900321317</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.753029579116529</v>
+        <v>1.766072475410894</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-3.786249592701154</v>
+        <v>-3.773183338400678</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.6170693551191135</v>
+        <v>-0.6038883458238757</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>4.776476213244038</v>
+        <v>4.789674952198801</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>2.10816921003434</v>
+        <v>2.121574337687171</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.732947750646922</v>
+        <v>-1.719490456936704</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-3.516746411483211</v>
+        <v>-3.503294122763101</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-2.118819204246392</v>
+        <v>-2.10526315789479</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>3.585447582575455</v>
+        <v>3.575017946877303</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>48</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>3.756561679790082</v>
+        <v>3.769083969465704</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-4.105011933174296</v>
+        <v>-4.092102123598245</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-6.583213973104215</v>
+        <v>-6.570206841686613</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-6.452960840496651</v>
+        <v>-6.439981698098187</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-9.074715388902213</v>
+        <v>-9.061604584527274</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-2.527273451186495</v>
+        <v>-2.51423055489213</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.528673835125467</v>
+        <v>-0.5156075808249909</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1.087476099426446</v>
+        <v>1.100657108721684</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>3.109809546577445</v>
+        <v>3.123008285532208</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.906982305117175</v>
+        <v>-1.893577177464344</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-2.111735629434691</v>
+        <v>-2.098278335724473</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-6.244019138755988</v>
+        <v>-6.230566850035878</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-6.664273749700804</v>
+        <v>-6.650717703349201</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-8.497885750757966</v>
+        <v>-8.508315386456118</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>34</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.480916030534353</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.718517478590478</v>
+        <v>4.731427288166529</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>10.20600171317035</v>
+        <v>10.21900884458795</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>16.21860778695433</v>
+        <v>16.23158692935279</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>15.68018657188216</v>
+        <v>15.6932973762571</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>13.03645203900959</v>
+        <v>13.04949493530395</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>18.83407126291373</v>
+        <v>18.84713751721421</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>12.48453492295581</v>
+        <v>12.49771593225105</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>6.541182095597073</v>
+        <v>6.554380834551836</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>2.749880439980871</v>
+        <v>2.763285567633702</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.3960493549249477</v>
+        <v>-0.38259206121473</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-6.244019138755988</v>
+        <v>-6.230566850035878</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>5.10043213265201</v>
+        <v>5.113988179003613</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-3.47337594683632</v>
+        <v>-3.483805582534472</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>31</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>12.02269071204809</v>
+        <v>12.03521300172371</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.73369774424512</v>
+        <v>0.7466075538211712</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>3.564635489261441</v>
+        <v>3.577642620679043</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3.694888621868941</v>
+        <v>3.707867764267405</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>3.156467406796814</v>
+        <v>3.169578211171753</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-6.223510010326237</v>
+        <v>-6.210467114031871</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-3.082437275985619</v>
+        <v>-3.069371021685143</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-3.549620674767162</v>
+        <v>-3.536439665471924</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-10.06223346417527</v>
+        <v>-10.04903472522051</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-7.686552197590288</v>
+        <v>-7.673147069937457</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>1.786113832930845</v>
+        <v>1.799571126641062</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>5.04630344188913</v>
+        <v>5.05975573060924</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>1.400242379331374</v>
+        <v>1.413798425682977</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>4.875770163220558</v>
+        <v>4.865340527522406</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>24</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>14.17322834645667</v>
+        <v>14.18575063613229</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>16.72832140015912</v>
+        <v>16.74123120973518</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>12.16678602689583</v>
+        <v>12.17979315831344</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>12.29703915950333</v>
+        <v>12.3100183019018</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>3.42528461109778</v>
+        <v>3.438395415472719</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>7.889393215480133</v>
+        <v>7.902436111774499</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>7.804659498207833</v>
+        <v>7.817725752508309</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.9958572339069462</v>
+        <v>-0.9826762246117084</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>3.109809546577424</v>
+        <v>3.123008285532187</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>2.259684361549461</v>
+        <v>2.273089489202292</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>2.054931037231917</v>
+        <v>2.068388330942135</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>6.255980861244048</v>
+        <v>6.269433149964158</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-6.664273749700889</v>
+        <v>-6.650717703349287</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-10.5812190840913</v>
+        <v>-10.59164871978945</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>26</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-10.18574601251764</v>
+        <v>-10.17322372284202</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.258858087020414</v>
+        <v>-0.2459482774443629</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>7.038580898690718</v>
+        <v>7.05158803010832</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.5234736610094473</v>
+        <v>-0.5104945186109831</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>2.784258970072173</v>
+        <v>2.797369774447112</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>6.927854753941681</v>
+        <v>6.940897650236046</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>6.84312103666943</v>
+        <v>6.856187290969906</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>2.529783791734076</v>
+        <v>2.542964801029314</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>10.16109159785947</v>
+        <v>10.17429033681424</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>5.464812566677722</v>
+        <v>5.478217694330553</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>1.413905396206268</v>
+        <v>1.427362689916485</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>1.448288553551734</v>
+        <v>1.461740842271844</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>4.874187788760651</v>
+        <v>4.887743835112254</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>1.27775527488312</v>
+        <v>1.267325639184968</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Hash Rate MA Ratio-90 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Hash Rate MA Ratio-90 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2214,101 +2214,101 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4006</v>
+        <v>4007</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.007183725074916936</v>
+        <v>0.006646158520375423</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.225500759707792</v>
+        <v>0.224892153585202</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.2424643938363431</v>
+        <v>0.2418472482420952</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.2618465964223304</v>
+        <v>0.2612256705849063</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.3098840299438379</v>
+        <v>0.3092453490717162</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.2224774207616846</v>
+        <v>0.2218632599687993</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.2261646066055931</v>
+        <v>0.2255483733354708</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.2711750027165181</v>
+        <v>0.2705424812608754</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.2738584121969723</v>
+        <v>0.2732243041430209</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.1857026491637868</v>
+        <v>0.1850815111419948</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.1945335981365446</v>
+        <v>0.1939078654392219</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.2679569091482037</v>
+        <v>0.2673129204804567</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.3359758135633939</v>
+        <v>0.3353102407624888</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.3752628596597773</v>
+        <v>0.3756168987115345</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.01139</t>
+          <t>X &gt; -0.01138</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3993</v>
+        <v>3994</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.07770496486241285</v>
+        <v>0.0771074284124964</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.3019793277496134</v>
+        <v>0.3013077615740585</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.3452742053840225</v>
+        <v>0.3445871658040858</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.3643220306832902</v>
+        <v>0.3636313555148618</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.4142901083492134</v>
+        <v>0.4135806931811743</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.3256591489967917</v>
+        <v>0.3249748424092189</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.3296594982078886</v>
+        <v>0.3289729407113171</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.3513545690437923</v>
+        <v>0.3506571087216344</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.3542651076913117</v>
+        <v>0.3535659249420391</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.2185701925894392</v>
+        <v>0.2178952254037654</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.2281042104050854</v>
+        <v>0.2274242745665234</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.3016629638722961</v>
+        <v>0.3009646814956568</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.3712795802941002</v>
+        <v>0.3705588923954011</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.38484653073467</v>
+        <v>0.3852332698617289</v>
       </c>
     </row>
     <row r="8">
@@ -2318,517 +2318,517 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3971</v>
+        <v>3972</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.06680264364544541</v>
+        <v>0.06613541237656761</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.3263212327810763</v>
+        <v>0.3255685591327406</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.3971560252216477</v>
+        <v>0.3963803204190626</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.3653637010758146</v>
+        <v>0.3645972404586431</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.3683331873122455</v>
+        <v>0.3675589422248535</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.2775560704688544</v>
+        <v>0.2768079710710154</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.2820350638187534</v>
+        <v>0.2812844355945643</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.3064225414681303</v>
+        <v>0.3056596225476724</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.3096754084151101</v>
+        <v>0.3089105569260298</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.1527661225557821</v>
+        <v>0.1520297977200968</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.1383063098371835</v>
+        <v>0.1375707208792392</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.2372292881254623</v>
+        <v>0.2364688822238108</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.259190500047346</v>
+        <v>0.2584189691903518</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.2714208890473273</v>
+        <v>0.2718960939064488</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.00875</t>
+          <t>X &gt; -0.008749</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3943</v>
+        <v>3944</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.1102017202349259</v>
+        <v>0.1094301913509099</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.3829779530457458</v>
+        <v>0.3821142565838258</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.4065432347865894</v>
+        <v>0.4056675788781305</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.3736054804410287</v>
+        <v>0.3727395967930605</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.3551091725013578</v>
+        <v>0.3542399217549317</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.2868875207193469</v>
+        <v>0.2860393506409338</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.2666848146635914</v>
+        <v>0.2658401539257227</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.3198767071751831</v>
+        <v>0.3190115391013819</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.4249057978438913</v>
+        <v>0.4240127592386074</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.2476076788368786</v>
+        <v>0.2467470373279568</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.234522184385149</v>
+        <v>0.2336615342188821</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.3846247142224684</v>
+        <v>0.3837261048551568</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.3590528223072269</v>
+        <v>0.3581542865113008</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.394983468956319</v>
+        <v>0.395504762293065</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.007432</t>
+          <t>X &gt; -0.007431</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3891</v>
+        <v>3892</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.01680758142936867</v>
+        <v>0.01588294513785371</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.4683931398465191</v>
+        <v>0.4673241059100235</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.57444022132605</v>
+        <v>0.5733365864456559</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.4624668276226274</v>
+        <v>0.4613936649634809</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.3227205085337346</v>
+        <v>0.3216732074919264</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.3009089887553671</v>
+        <v>0.2998720092104321</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.2815707347394465</v>
+        <v>0.2805367296820052</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.3673708902911557</v>
+        <v>0.3663061595169097</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.3976261105746772</v>
+        <v>0.396552037135983</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.2293035314254084</v>
+        <v>0.2282571825630413</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.2444533792966368</v>
+        <v>0.243399028417528</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.3704170287241126</v>
+        <v>0.3693304278274994</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.3501147395077453</v>
+        <v>0.3490254253432425</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.4088862872785626</v>
+        <v>0.4095503209779636</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.006114</t>
+          <t>X &gt; -0.006113</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>3837</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.001364174592517031</v>
+        <v>0.01388646426813978</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.2230358963032799</v>
+        <v>0.2099514246212024</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.5560070649341426</v>
+        <v>0.5573282597175009</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.4405649005329906</v>
+        <v>0.4275430028898555</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.358531251756709</v>
+        <v>0.3456342537909407</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.4102048700067016</v>
+        <v>0.3972331981428994</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.2214128801017452</v>
+        <v>0.2227478706452359</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.3930316549819466</v>
+        <v>0.3801913267804338</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.4245761611878649</v>
+        <v>0.4117467897834501</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.2398110646649982</v>
+        <v>0.2271813055695873</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.2580560372319098</v>
+        <v>0.2454716642754633</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.4374083163104387</v>
+        <v>0.4248121549133259</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.4227507422219858</v>
+        <v>0.4102515514709282</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.5049159172118323</v>
+        <v>0.4944862815136801</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.004796</t>
+          <t>X &gt; -0.004795</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3752</v>
+        <v>3753</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.2444670492743413</v>
+        <v>0.242974482354299</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.4017681784981946</v>
+        <v>0.4001892107984091</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.7779709954325824</v>
+        <v>0.7909781268501845</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.6303724928366847</v>
+        <v>0.6287278649612773</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.5588307669903685</v>
+        <v>0.5571897417139127</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.6581531941922449</v>
+        <v>0.6564930418091137</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.4403699825080523</v>
+        <v>0.4534362368085283</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.6266696048828706</v>
+        <v>0.6250051661990099</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.6603952760768834</v>
+        <v>0.6587194025581766</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.5708250628366685</v>
+        <v>0.5691491271149971</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.4193340554298715</v>
+        <v>0.4327913491400892</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.6552882666782196</v>
+        <v>0.6535876106831608</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.5965842305815556</v>
+        <v>0.5948869849831553</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.7016522734069497</v>
+        <v>0.7026491752278972</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.003478</t>
+          <t>X &gt; -0.003477</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>3630</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.4331898743489688</v>
+        <v>0.4311718815535599</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.4029594796899758</v>
+        <v>0.400890456781049</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.8327196900807436</v>
+        <v>0.8457268214983458</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.5932539885749222</v>
+        <v>0.5911251371592741</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.620004083045032</v>
+        <v>0.6178473447184913</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.7676600655489523</v>
+        <v>0.7654724154049006</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.6003953991707505</v>
+        <v>0.6134616534712265</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.6437501775771892</v>
+        <v>0.6415787043199828</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.6806876087849574</v>
+        <v>0.6785026902285765</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.6719457418725483</v>
+        <v>0.6697313829540406</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.3295272193170788</v>
+        <v>0.3429845130272966</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.599825532133579</v>
+        <v>0.5976269825632414</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.6084535230263839</v>
+        <v>0.6062363038112792</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.8857230646690653</v>
+        <v>0.8752934289709131</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.00216</t>
+          <t>X &gt; -0.002159</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>3468</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.5560438431962353</v>
+        <v>0.5533088759942615</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.5424700812142618</v>
+        <v>0.5396585208206872</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.9533567703011201</v>
+        <v>0.9663639017187222</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.8405049050416267</v>
+        <v>0.8375962395516865</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.00902585305964</v>
+        <v>1.006040781045606</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.005752662484774</v>
+        <v>1.00278163437747</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.863415258576552</v>
+        <v>0.876481512877028</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.9596310979858842</v>
+        <v>0.9566478921317696</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.087715406327661</v>
+        <v>1.084690797776496</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.7851406535763914</v>
+        <v>0.7985457812292225</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.4362951102386319</v>
+        <v>0.4497524039488496</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.6888145308894451</v>
+        <v>0.6858596629324225</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.8616778073925317</v>
+        <v>0.8586509907988784</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.053729012794548</v>
+        <v>1.043299377096396</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.0008421</t>
+          <t>X &gt; -0.0008412</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>3267</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.7767328289342785</v>
+        <v>0.7729794781732551</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.618314266764628</v>
+        <v>0.6144993433944848</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.9877378255303171</v>
+        <v>1.000744956947919</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.196121728310679</v>
+        <v>1.192113481765254</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.9940919505473857</v>
+        <v>1.007202754922325</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.9415498383006025</v>
+        <v>0.9376043074931886</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.9791776994926877</v>
+        <v>0.9922439537931638</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.9574271398180727</v>
+        <v>0.9534408346316923</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1.202424805655347</v>
+        <v>1.215623544610111</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.6582971726470035</v>
+        <v>0.6717023002998346</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.3617445827235528</v>
+        <v>0.3752018764337706</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.750165128155551</v>
+        <v>0.7461773360106321</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.095138555165967</v>
+        <v>1.10869460151757</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.161205158332976</v>
+        <v>1.150775522634824</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; 0.000476</t>
+          <t>X &gt; 0.0004767</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3041</v>
+        <v>3040</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.004098625602829</v>
+        <v>1.016620915278452</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.7898632310833165</v>
+        <v>0.7699215294898636</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.380539859572139</v>
+        <v>1.411910586290219</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.477941481010134</v>
+        <v>1.476411116010688</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.136629332955039</v>
+        <v>1.135295404518679</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.091003468519936</v>
+        <v>1.071184057880345</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.203443592851329</v>
+        <v>1.202012406025787</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.34635183907136</v>
+        <v>1.326659738570413</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.6798292704433</v>
+        <v>1.67885614259675</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.092688963784859</v>
+        <v>1.092008704372773</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.052301188448219</v>
+        <v>1.051727144928755</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.138420848090448</v>
+        <v>1.118989217047321</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.573148150989674</v>
+        <v>1.572966507177028</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.39537852634389</v>
+        <v>1.371070578456191</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 0.001794</t>
+          <t>X &gt; 0.001795</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2738</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.428487984058542</v>
+        <v>1.42134509273334</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.239752751247508</v>
+        <v>1.252662560823559</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.683993858587442</v>
+        <v>1.697000990005044</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.412933601920948</v>
+        <v>1.425912744319412</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.9109954222373275</v>
+        <v>0.9241062266122668</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.009831171684553</v>
+        <v>1.002582043916085</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.363053658791834</v>
+        <v>1.37611991309231</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.610020823778349</v>
+        <v>1.602481926239875</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.87760801317107</v>
+        <v>1.890806752125833</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.173521528398716</v>
+        <v>1.186926656051547</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.297355279656159</v>
+        <v>1.310812573366377</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.316243826912384</v>
+        <v>1.308681050657803</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.84558746286303</v>
+        <v>1.859143509214633</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.73007870017949</v>
+        <v>1.719649064481338</v>
       </c>
     </row>
     <row r="18">
@@ -2841,46 +2841,46 @@
         <v>2452</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.807417774368091</v>
+        <v>1.797812575822611</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.378070007306803</v>
+        <v>1.390979816882854</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.716996653339656</v>
+        <v>1.730003784757258</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.765716968988329</v>
+        <v>1.778696111386793</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.186529345436746</v>
+        <v>1.199640149811685</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.22136711433825</v>
+        <v>1.211649320090878</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.829944979447696</v>
+        <v>1.843011233748172</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.852157991759178</v>
+        <v>1.865339001054416</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.443686653700858</v>
+        <v>2.456885392655622</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.675127537188423</v>
+        <v>1.688532664841254</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.878204555448335</v>
+        <v>1.891661849158552</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.871804678536023</v>
+        <v>1.885256967256133</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>2.185644684230589</v>
+        <v>2.199200730582191</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.864403536898394</v>
+        <v>1.853973901200241</v>
       </c>
     </row>
     <row r="19">
@@ -2893,46 +2893,46 @@
         <v>2154</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>2.288362979697176</v>
+        <v>2.275464479906489</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.837420750205531</v>
+        <v>1.850330559781582</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2.417482405725927</v>
+        <v>2.430489537143529</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.89778196358877</v>
+        <v>1.910761105987234</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.498636514533317</v>
+        <v>1.511747318908256</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.285400643521022</v>
+        <v>1.298443539815388</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.850620500993408</v>
+        <v>1.863686755293884</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.61556337890643</v>
+        <v>1.628744388201667</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2.111666556790979</v>
+        <v>2.124865295745742</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.493667648457574</v>
+        <v>1.507072776110405</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2.031718409562465</v>
+        <v>2.045175703272683</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.019676311568993</v>
+        <v>2.033128600289103</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.249375275368749</v>
+        <v>2.262931321720352</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.988418798917088</v>
+        <v>1.977989163218936</v>
       </c>
     </row>
     <row r="20">
@@ -2945,46 +2945,46 @@
         <v>1849</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.91434967330003</v>
+        <v>1.926871962975653</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.763024843461785</v>
+        <v>1.775934653037837</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2.828404919991215</v>
+        <v>2.841412051408817</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.03924215211196</v>
+        <v>2.052221294510424</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.446737648775866</v>
+        <v>1.459848453150805</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.419679856907962</v>
+        <v>1.432722753202327</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.875779022274948</v>
+        <v>1.888845276575424</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.138179182173815</v>
+        <v>1.151360191469053</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2.0506784847422</v>
+        <v>2.063877223696963</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.092386723186415</v>
+        <v>1.105791850839246</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.374382993244168</v>
+        <v>1.387840286954386</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.246516285797824</v>
+        <v>1.259968574517934</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.745677575339677</v>
+        <v>1.75923362169128</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.29231616018491</v>
+        <v>1.281886524486758</v>
       </c>
     </row>
     <row r="21">
@@ -2997,46 +2997,46 @@
         <v>1528</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.825933407538713</v>
+        <v>1.838455697214336</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.9342550825325731</v>
+        <v>0.9471648921086242</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3.222632449234411</v>
+        <v>3.235639580652013</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2.632990293883793</v>
+        <v>2.645969436282257</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.440118817031518</v>
+        <v>1.453229621406457</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.279445571501114</v>
+        <v>1.292488467795479</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.45649195894088</v>
+        <v>1.469558213241356</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.120198612515388</v>
+        <v>1.133379621810626</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.713648988113192</v>
+        <v>1.726847727067955</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.125303907797317</v>
+        <v>1.138709035450148</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.247775714369787</v>
+        <v>1.261233008080005</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.7585986622911278</v>
+        <v>0.7720509510112379</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.712689601084449</v>
+        <v>1.726245647436052</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.6535104098005249</v>
+        <v>0.6430807741023727</v>
       </c>
     </row>
     <row r="22">
@@ -3049,46 +3049,46 @@
         <v>1234</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.882574645754374</v>
+        <v>1.895096935429997</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.4330755870850851</v>
+        <v>0.4459853966611362</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>3.522809797830476</v>
+        <v>3.535816929248078</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.761652881815614</v>
+        <v>2.774632024214078</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2.061157112448463</v>
+        <v>2.074267916823402</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.358599050164123</v>
+        <v>2.371641946458489</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.8686789471544</v>
+        <v>1.881745201454876</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.8342346083404877</v>
+        <v>0.8474156176357255</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.259458385043111</v>
+        <v>1.272657123997874</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.138668694342584</v>
+        <v>1.152073821995415</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.4476917071400734</v>
+        <v>0.4611490008502912</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.5714097384318393</v>
+        <v>-0.5579574497117292</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.034267579310452</v>
+        <v>1.047823625662055</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.06842975437442078</v>
+        <v>0.05800011867626864</v>
       </c>
     </row>
     <row r="23">
@@ -3101,46 +3101,46 @@
         <v>1037</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.701354350956848</v>
+        <v>1.713876640632471</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.8612368614255743</v>
+        <v>0.8741466710016255</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3.455760633131781</v>
+        <v>3.468767764549384</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>3.007421673164544</v>
+        <v>3.020400815563008</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2.276136427234135</v>
+        <v>2.289247231609075</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.670010380378919</v>
+        <v>2.683053276673284</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2.392412632248387</v>
+        <v>2.405478886548863</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.9609090791756643</v>
+        <v>0.9740900884709021</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.7070451621351239</v>
+        <v>0.7202439010898871</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.7248081159692887</v>
+        <v>0.7382132436221198</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.2514013317812669</v>
+        <v>-0.2379440380710491</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.084906313297928</v>
+        <v>-1.071454024577818</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.3270473689104918</v>
+        <v>0.3406034152620947</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.483983468533566</v>
+        <v>-0.4944131042317181</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>844</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.534997698747375</v>
+        <v>1.547519988422998</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.3973577350722124</v>
+        <v>0.4102675446482635</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2.609124099565669</v>
+        <v>2.622131230983271</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2.502410407528622</v>
+        <v>2.515389549927086</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2.674889666390101</v>
+        <v>2.68800047076504</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2.616881367138937</v>
+        <v>2.629924263433303</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.532147649866658</v>
+        <v>2.545213904167134</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.9986135401846781</v>
+        <v>1.011794549479916</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.411547303291485</v>
+        <v>1.424746042246248</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.5614221182635575</v>
+        <v>0.5748272459163886</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.2381853816236941</v>
+        <v>0.2516426753339118</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.5568153472867934</v>
+        <v>-0.5433630585666833</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>1.274114875891527</v>
+        <v>1.28767092224313</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.1020352603005108</v>
+        <v>0.09160562460235866</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>697</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.604122655399784</v>
+        <v>3.616644945075407</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.992549042435527</v>
+        <v>2.005458852011579</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>4.323648771993888</v>
+        <v>4.33665590341149</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>3.880013812779289</v>
+        <v>3.892992955177753</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.915480689529218</v>
+        <v>3.928591493904158</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.778202397689633</v>
+        <v>2.791245293983998</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.54999665746184</v>
+        <v>2.563062911762316</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.6480930291250999</v>
+        <v>0.6612740384203377</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1.734869326586988</v>
+        <v>1.748068065541752</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.5978000956480187</v>
+        <v>0.6112052233008498</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.966934863152531</v>
+        <v>0.9803921568627487</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.1464581631462281</v>
+        <v>-0.133005874426118</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.011479478419631</v>
+        <v>1.025035524771233</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.1735194188593283</v>
+        <v>-0.1839490545574805</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>582</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>4.379413913466998</v>
+        <v>4.39193620314262</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>3.455125523870436</v>
+        <v>3.468035333446487</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>5.809397710744641</v>
+        <v>5.822404842162243</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>4.908723008300598</v>
+        <v>4.921702150699062</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>4.8857657107542</v>
+        <v>4.898876515129139</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>4.495922425102165</v>
+        <v>4.508965321396531</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>3.380260872778344</v>
+        <v>3.39332712707882</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.8512218038937434</v>
+        <v>0.8644028131889812</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.477507141079137</v>
+        <v>1.4907058800339</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.9710245677350571</v>
+        <v>0.9844296953878882</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>1.109913855101325</v>
+        <v>1.123371148811543</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.4570117890790613</v>
+        <v>0.4704640777991713</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1.754970236553412</v>
+        <v>1.768526282905015</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.4582998162523708</v>
+        <v>0.4478701805542187</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>471</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>4.619088219068153</v>
+        <v>4.631610508743776</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>4.281399956422369</v>
+        <v>4.29430976599842</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>5.37273082519733</v>
+        <v>5.385737956614932</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>3.804470157380202</v>
+        <v>3.817449299778666</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3.266048942308032</v>
+        <v>3.279159746682971</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>3.351176654970615</v>
+        <v>3.364219551264981</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.054128712645259</v>
+        <v>3.067194966945735</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.737688413651441</v>
+        <v>1.750869422946678</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2.313631202628372</v>
+        <v>2.326829941583135</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.4019348923350563</v>
+        <v>0.4153400199878874</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.1971815680174771</v>
+        <v>0.2106388617276949</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.01925050030983044</v>
+        <v>0.0327027890299405</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.8728812396833945</v>
+        <v>0.8864372860349974</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.06103144669429383</v>
+        <v>0.05060181099614169</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>372</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3.151722970112601</v>
+        <v>3.164245259788224</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>2.077783765750496</v>
+        <v>2.090693575326547</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3.833452693562514</v>
+        <v>3.846459824980116</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>3.157254213266789</v>
+        <v>3.170233355665253</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.350015793893547</v>
+        <v>2.363126598268487</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2.109823323007056</v>
+        <v>2.122866219301422</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2.025089605734777</v>
+        <v>2.038155860035253</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1.826723411254349</v>
+        <v>1.839904420549587</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.6904547078677368</v>
+        <v>0.7036534468225</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.234939294364487</v>
+        <v>-1.221534166711656</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-2.246144231585291</v>
+        <v>-2.232686937875073</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-2.480578278540939</v>
+        <v>-2.467125989820829</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.7502952550772406</v>
+        <v>-0.7367392087256377</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-2.113477148607402</v>
+        <v>-2.123906784305554</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>301</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1.991611513677071</v>
+        <v>2.004133803352694</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>2.705619296061641</v>
+        <v>2.718529105637693</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>4.304106071192628</v>
+        <v>4.31711320261023</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>3.437681462936347</v>
+        <v>3.450660605334811</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2.899260247864177</v>
+        <v>2.912371052239116</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.867798531094792</v>
+        <v>1.880841427389157</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>1.450838900201248</v>
+        <v>1.463905154501724</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.01302223944404801</v>
+        <v>0.0001587698511897884</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.4062480392476004</v>
+        <v>-0.3930493002928372</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.256373224275528</v>
+        <v>-1.242968096622697</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-2.457804289456902</v>
+        <v>-2.444346995746685</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-3.087872959353987</v>
+        <v>-3.074420670633877</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-1.846998002192578</v>
+        <v>-1.833441955840975</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-3.258406238022602</v>
+        <v>-3.268835873720754</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>246</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.791114525318484</v>
+        <v>2.803636814994107</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3.212061237557471</v>
+        <v>3.224971047133522</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>4.036704726082831</v>
+        <v>4.049711857500434</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3.760453793649688</v>
+        <v>3.773432936048152</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>2.002520383455561</v>
+        <v>2.0156311878305</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.893458256130579</v>
+        <v>1.906501152424944</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>2.621732668939593</v>
+        <v>2.634798923240069</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.1220289449548488</v>
+        <v>0.1352099542500866</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.564987201390053</v>
+        <v>-1.55178846243529</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-2.008608321377338</v>
+        <v>-1.995203193724507</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-2.61986571073556</v>
+        <v>-2.606408417025342</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-2.991986618430786</v>
+        <v>-2.978534329710676</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-1.78622496921308</v>
+        <v>-1.772668922861477</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-4.788536157262001</v>
+        <v>-4.798965792960153</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>198</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.557066730295077</v>
+        <v>2.569589019970699</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.985897157734861</v>
+        <v>4.998806967310912</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>6.611230471340292</v>
+        <v>6.624237602757894</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>6.236433098897287</v>
+        <v>6.249412241295751</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>4.6879108737241</v>
+        <v>4.701021678099039</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>2.965150791237747</v>
+        <v>2.978193687532112</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>3.385467579015966</v>
+        <v>3.398533833316442</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.1120188500685586</v>
+        <v>-0.09883784077332081</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-2.698271261503379</v>
+        <v>-2.685072522548616</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-2.033244931379798</v>
+        <v>-2.019839803726967</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-2.743048760747882</v>
+        <v>-2.729591467037665</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-2.203615098351946</v>
+        <v>-2.190162809631836</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.6036676890948343</v>
+        <v>-0.5901116427432314</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-3.889299892172069</v>
+        <v>-3.899729527870221</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>164</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.604122655399784</v>
+        <v>3.616644945075407</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>5.041329530240397</v>
+        <v>5.054239339816448</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>5.865973018765764</v>
+        <v>5.878980150183367</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.166957858690331</v>
+        <v>4.179937001088796</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>2.409024448496211</v>
+        <v>2.422135252871151</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.8771980935289534</v>
+        <v>0.8902409898233188</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.1827082786956993</v>
+        <v>0.1957745329961753</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-2.723499510329709</v>
+        <v>-2.710318501034472</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-4.613767689194937</v>
+        <v>-4.600568950240174</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-3.024868483978956</v>
+        <v>-3.011463356326125</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-3.229621808296535</v>
+        <v>-3.216164514586318</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-1.365970358268179</v>
+        <v>-1.352518069548069</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-1.78622496921308</v>
+        <v>-1.772668922861477</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-3.975528027180701</v>
+        <v>-3.985957662878853</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>133</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.641900025654685</v>
+        <v>1.654422315330308</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>6.045364006675392</v>
+        <v>6.058273816251443</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>6.402374999326923</v>
+        <v>6.415382130744526</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4.276989034190059</v>
+        <v>4.289968176588523</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>2.234808420621647</v>
+        <v>2.247919224996586</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>2.532250358337308</v>
+        <v>2.545293254631673</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.9437572425687861</v>
+        <v>0.9568234968692622</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-2.530944953205193</v>
+        <v>-2.517763943909955</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-3.343824538635609</v>
+        <v>-3.330625799680845</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-1.938310625919179</v>
+        <v>-1.924905498266348</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-4.398703047981115</v>
+        <v>-4.385245754270898</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-2.860560492139442</v>
+        <v>-2.847108203419332</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-2.528935403836229</v>
+        <v>-2.515379357484626</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-6.038612567800541</v>
+        <v>-6.049042203498693</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>109</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-1.117291531219145</v>
+        <v>-1.104769241543522</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>3.693153204440442</v>
+        <v>3.706063014016493</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>5.133146883164954</v>
+        <v>5.146154014582557</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>2.511106437790808</v>
+        <v>2.524085580189272</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1.972685222718638</v>
+        <v>1.985796027093578</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.352695967773741</v>
+        <v>1.365738864068106</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.5669001348196332</v>
+        <v>-0.5538338805191572</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-2.868945918922236</v>
+        <v>-2.855764909626998</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-4.76480819042564</v>
+        <v>-4.751609451470877</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-2.862639797471907</v>
+        <v>-2.849234669819076</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-5.819686699771147</v>
+        <v>-5.806229406060929</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-4.867872349765157</v>
+        <v>-4.854420061045047</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-1.618402190067862</v>
+        <v>-1.604846143716259</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-5.038405628433772</v>
+        <v>-5.048835264131924</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>83</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1.723429149669542</v>
+        <v>1.735951439345165</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>4.931132645139023</v>
+        <v>4.944042454715074</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>4.536263938542433</v>
+        <v>4.549271069960035</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>3.461697794041491</v>
+        <v>3.474676936439955</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>1.718457301860902</v>
+        <v>1.731568106235841</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.3937393146403139</v>
+        <v>-0.3806964183459485</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-2.888111586129462</v>
+        <v>-2.875045331828986</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-4.560114262019397</v>
+        <v>-4.546933252724159</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-9.440391256635429</v>
+        <v>-9.427192517680666</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-5.471239333229626</v>
+        <v>-5.457834205576795</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-8.085631211764067</v>
+        <v>-8.072173918053849</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-6.846428777310209</v>
+        <v>-6.832976488590099</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-3.6522255569298</v>
+        <v>-3.638669510578197</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-7.016962055978823</v>
+        <v>-7.027391691676975</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Hash Rate MA Ratio-90 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Hash Rate MA Ratio-90 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3911,98 +3911,98 @@
         <v>83</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1.723429149669542</v>
+        <v>1.735951439345165</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-8.32187940305375</v>
+        <v>-8.308969593477698</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-13.53602521808408</v>
+        <v>-13.52301808666648</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-8.58649497704284</v>
+        <v>-8.573515834644375</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-10.32973546922344</v>
+        <v>-10.3166246648485</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-6.417835700182479</v>
+        <v>-6.404792803888114</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-8.912207971671627</v>
+        <v>-8.899141717371151</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-12.99384920177842</v>
+        <v>-12.98066819248319</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-9.440391256635429</v>
+        <v>-9.427192517680666</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-6.67605861033806</v>
+        <v>-6.662653482685229</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-5.675992657547205</v>
+        <v>-5.662535363836987</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-6.846428777310209</v>
+        <v>-6.832976488590099</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-6.061864111146676</v>
+        <v>-6.048308064795073</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-7.016962055978823</v>
+        <v>-7.027391691676975</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.01139</t>
+          <t>X &lt; -0.01138</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>96</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-1.451771653543311</v>
+        <v>-1.439249363867688</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-10.35501193317423</v>
+        <v>-10.34210212359818</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-15.95821397310415</v>
+        <v>-15.94520684168655</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-11.66129417382999</v>
+        <v>-11.64831503143153</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-13.24138205556882</v>
+        <v>-13.22827125119388</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-9.81894011785316</v>
+        <v>-9.805897221558794</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-11.98700716845878</v>
+        <v>-11.97394091415831</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-14.53752390057361</v>
+        <v>-14.52434289127837</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-11.47352378675591</v>
+        <v>-11.46032504780115</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-7.115315638450511</v>
+        <v>-7.10191051079768</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-6.278402296101419</v>
+        <v>-6.264945002391201</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-7.285685805422659</v>
+        <v>-7.272233516702549</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-6.664273749700889</v>
+        <v>-6.650717703349287</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-6.414552417424602</v>
+        <v>-6.424982053122754</v>
       </c>
     </row>
     <row r="8">
@@ -4015,514 +4015,514 @@
         <v>118</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.7985230659726881</v>
+        <v>-0.7860007762970653</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-9.189757695886094</v>
+        <v>-9.176847886310043</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-14.66937216519455</v>
+        <v>-14.65636503377695</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-9.454373269875184</v>
+        <v>-9.44139412747672</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-9.14533685782871</v>
+        <v>-9.13222605345377</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-6.305522038757118</v>
+        <v>-6.292479142462753</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-8.085171010266691</v>
+        <v>-8.072104755966215</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-10.24726966328547</v>
+        <v>-10.23408865399023</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-7.765896668111843</v>
+        <v>-7.75269792915708</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-3.531276090427902</v>
+        <v>-3.517870962775071</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-2.041114160508201</v>
+        <v>-2.027656866797983</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-3.70164625740005</v>
+        <v>-3.68819396867994</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-1.579527986989028</v>
+        <v>-1.565971940637425</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-1.329806654712741</v>
+        <v>-1.340236290410893</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.00875</t>
+          <t>X &lt; -0.008749</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>146</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-1.808506813360658</v>
+        <v>-1.795984523685036</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-8.899532481119444</v>
+        <v>-8.886622671543392</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-12.03412721511329</v>
+        <v>-12.02112008369568</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-7.7942850414099</v>
+        <v>-7.781305899011436</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-6.962843242783443</v>
+        <v>-6.949732438408503</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-5.295538291369148</v>
+        <v>-5.282495395074783</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-6.065203515490737</v>
+        <v>-6.052137261190261</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-8.587181434820188</v>
+        <v>-8.57400042552495</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-9.333112827851799</v>
+        <v>-9.319914088897036</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-5.388717464934523</v>
+        <v>-5.375312337281692</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-4.223607775553475</v>
+        <v>-4.210150481843257</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-6.928950645605305</v>
+        <v>-6.915498356885195</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-3.924547722303629</v>
+        <v>-3.910991675952026</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-4.359757896876658</v>
+        <v>-4.370187532574811</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.007432</t>
+          <t>X &lt; -0.007431</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>198</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.5368647100930559</v>
+        <v>0.5493869997686787</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-8.145415973578274</v>
+        <v>-8.132506164002223</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-12.0756382155284</v>
+        <v>-12.0626310841108</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-7.399930537466354</v>
+        <v>-7.386951395067889</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-4.402998217184987</v>
+        <v>-4.389887412810047</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-4.105556279469326</v>
+        <v>-4.09251338317496</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-4.69534050179211</v>
+        <v>-4.682274247491634</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-7.182725920775631</v>
+        <v>-7.169544911480394</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-6.233624796856923</v>
+        <v>-6.220426057902159</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-3.548396446531306</v>
+        <v>-3.534991318878475</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-3.248099265798388</v>
+        <v>-3.23464197208817</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-4.728867623604472</v>
+        <v>-4.715415334884362</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-2.623869709296848</v>
+        <v>-2.610313662945245</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-3.384249387121571</v>
+        <v>-3.394679022819723</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.006114</t>
+          <t>X &lt; -0.006113</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.6561679790026318</v>
+        <v>0.4602604400538866</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-2.530208783567936</v>
+        <v>-2.327396241245232</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-9.045335185225369</v>
+        <v>-8.996677429921846</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-5.35776979965344</v>
+        <v>-5.144049939568006</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-3.919906429745367</v>
+        <v>-3.713835555655827</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-4.808235243017855</v>
+        <v>-4.597563888225466</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-2.711213517665122</v>
+        <v>-2.713770310483767</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-5.956174694224408</v>
+        <v>-5.742228266772443</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-5.223523786755912</v>
+        <v>-5.012696589303125</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.899045797180662</v>
+        <v>-2.700560049664603</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-2.706973724672849</v>
+        <v>-2.510004290928748</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-4.656717551454392</v>
+        <v>-4.451910723553667</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-3.09284517827232</v>
+        <v>-2.895776991886834</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-4.033600036472215</v>
+        <v>-3.855812092648449</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.004796</t>
+          <t>X &lt; -0.004795</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>337</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-2.199320673151149</v>
+        <v>-2.186798383475526</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-3.810894286115406</v>
+        <v>-3.797984476539355</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-9.072152026201501</v>
+        <v>-9.192755861294394</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-5.992046386219371</v>
+        <v>-5.979067243820907</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-5.055541347604226</v>
+        <v>-5.042430543229287</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-6.23302566357588</v>
+        <v>-6.219982767281515</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-4.399482513626431</v>
+        <v>-4.534781622122907</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-6.937671829567691</v>
+        <v>-6.924490820272453</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-6.406955739418635</v>
+        <v>-6.393757000463872</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-5.777790983618161</v>
+        <v>-5.76438585596533</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-3.756147103223078</v>
+        <v>-3.898081097065756</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-5.798915281189224</v>
+        <v>-5.785462992469114</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-4.142018556822549</v>
+        <v>-4.128462510470946</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-5.07924084472431</v>
+        <v>-5.089670480422463</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.003478</t>
+          <t>X &lt; -0.003477</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-3.033395123665699</v>
+        <v>-3.020872833990076</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.701124244189351</v>
+        <v>-2.6882144346133</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-6.880833020723209</v>
+        <v>-6.970674804249548</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-3.93672707426289</v>
+        <v>-3.923747931864426</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-4.042247856434621</v>
+        <v>-4.029137052059681</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-5.259957433870483</v>
+        <v>-5.246914537576117</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-4.369960892247633</v>
+        <v>-4.465824031041421</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-5.054064030725456</v>
+        <v>-5.040883021430218</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-4.681224437515127</v>
+        <v>-4.668025698560363</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-4.880590403454121</v>
+        <v>-4.86718527580129</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.930576209144903</v>
+        <v>-2.035010078313107</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-3.635323486582081</v>
+        <v>-3.621871197861971</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.968621575787843</v>
+        <v>-2.95506552943624</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-4.998430413067304</v>
+        <v>-4.903242922687973</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.00216</t>
+          <t>X &lt; -0.002159</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-2.812927138101351</v>
+        <v>-2.800404848425728</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-2.667312252663045</v>
+        <v>-2.654402443086994</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-5.539880639770821</v>
+        <v>-5.605084370973024</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-4.129627507163327</v>
+        <v>-4.116648364764863</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-4.988048722235497</v>
+        <v>-4.974937917860558</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-5.01060678451983</v>
+        <v>-4.997563888225464</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-4.535084091535701</v>
+        <v>-4.602274247491629</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-5.322780310830019</v>
+        <v>-5.309599301534782</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-5.54403660726873</v>
+        <v>-5.530837868313967</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-4.067228426037452</v>
+        <v>-4.137166921054082</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.937566283239683</v>
+        <v>-2.011333445408859</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-3.0285850551547</v>
+        <v>-3.01513276643459</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-3.448839666099602</v>
+        <v>-3.435283619747999</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-4.401669969759546</v>
+        <v>-4.334949898781915</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.0008421</t>
+          <t>X &lt; -0.0008412</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.854884103342506</v>
+        <v>-2.842361813666884</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.177301089800736</v>
+        <v>-2.164391280224685</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-4.077685223606771</v>
+        <v>-4.125427725220689</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-4.309313876282744</v>
+        <v>-4.296334733884279</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-3.458773359916655</v>
+        <v>-3.507724407607235</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-3.282104369060896</v>
+        <v>-3.269061472766531</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-3.667529135407584</v>
+        <v>-3.716090672612403</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-3.771955581347498</v>
+        <v>-3.758774572052261</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-4.376066159637269</v>
+        <v>-4.424351649977687</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.376679274814144</v>
+        <v>-2.4282825850511</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.059955694159669</v>
+        <v>-1.113429850876052</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.360523993124922</v>
+        <v>-2.347071704404811</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.322839970843049</v>
+        <v>-3.374018674223066</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-3.494844388227527</v>
+        <v>-3.448068322867591</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; 0.000476</t>
+          <t>X &lt; 0.0004767</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.729956768648954</v>
+        <v>-2.764469905770653</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-2.07095327659902</v>
+        <v>-2.012707038532021</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-4.121092760982947</v>
+        <v>-4.203319633116919</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-3.943087222803136</v>
+        <v>-3.930915157574695</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.915638855062817</v>
+        <v>-2.906301554224186</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-2.807950238030266</v>
+        <v>-2.749222655997976</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-3.318322458107403</v>
+        <v>-3.307866664553245</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-3.880472618522333</v>
+        <v>-3.821069646496589</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-4.558124547212181</v>
+        <v>-4.546188425410264</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.981355917549777</v>
+        <v>-2.973824091044584</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.754592772291886</v>
+        <v>-2.747834736231503</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.815447710184564</v>
+        <v>-2.757683881434545</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-3.756742767813385</v>
+        <v>-3.748719606298856</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-3.170277608264293</v>
+        <v>-3.091648719789418</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 0.001794</t>
+          <t>X &lt; 0.001795</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.750602170320192</v>
+        <v>-2.73807988064457</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-2.340306050821283</v>
+        <v>-2.365430558572463</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-3.506503156327106</v>
+        <v>-3.530991155412046</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-2.602322647074949</v>
+        <v>-2.627435708399879</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.555064197548681</v>
+        <v>-1.581241305194865</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.773466032861755</v>
+        <v>-1.76042313656739</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-2.630443746629872</v>
+        <v>-2.655745139164445</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-3.2451197707801</v>
+        <v>-3.231938761484862</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-3.56300718158986</v>
+        <v>-3.587906168745107</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.233176298224016</v>
+        <v>-2.259505836750932</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.39813622071339</v>
+        <v>-2.424472328831378</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.289843233360571</v>
+        <v>-2.276390944640461</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-3.113977891712729</v>
+        <v>-3.14000077799821</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.824619034745105</v>
+        <v>-2.80072169809317</v>
       </c>
     </row>
     <row r="18">
@@ -4532,49 +4532,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-2.584402540949817</v>
+        <v>-2.571880251274195</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.920545913756754</v>
+        <v>-1.939282232755239</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.648028787918975</v>
+        <v>-2.666485158838654</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-2.425520581282392</v>
+        <v>-2.444080058753926</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.534188539864665</v>
+        <v>-1.553504139002712</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.601488243486394</v>
+        <v>-1.588445347192028</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.627213981110842</v>
+        <v>-2.645800083357898</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.758385130031911</v>
+        <v>-2.777080117555741</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-3.4573849317011</v>
+        <v>-3.475693276650816</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-2.386872615903279</v>
+        <v>-2.406163454362428</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-2.61986571073556</v>
+        <v>-2.639107098673961</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-2.491731158280089</v>
+        <v>-2.51105465491392</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.757069842496982</v>
+        <v>-2.776404097492062</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-2.230068605573656</v>
+        <v>-2.212527840668542</v>
       </c>
     </row>
     <row r="19">
@@ -4584,49 +4584,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-2.442103617951247</v>
+        <v>-2.429581328275624</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.922166529989845</v>
+        <v>-1.936044628731658</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.752706950151094</v>
+        <v>-2.766277719960819</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.927468124129909</v>
+        <v>-1.941437676172875</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.461546664622325</v>
+        <v>-1.47591478161376</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.239531128318085</v>
+        <v>-1.253942489048512</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.96619529066956</v>
+        <v>-1.980267042139083</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.787974699131055</v>
+        <v>-1.802278009712971</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.18228667335385</v>
+        <v>-2.196414692314292</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.561013592722468</v>
+        <v>-1.575707761656787</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.098835732633923</v>
+        <v>-2.113320453654737</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.984855483619178</v>
+        <v>-1.999400699365083</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.067166311684353</v>
+        <v>-2.081796691475262</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.737549833445271</v>
+        <v>-1.724568829982253</v>
       </c>
     </row>
     <row r="20">
@@ -4636,49 +4636,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2240</v>
+        <v>2241</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.494769878132743</v>
+        <v>-1.504873439584934</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.351903585039238</v>
+        <v>-1.362408381920417</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-2.389707383440303</v>
+        <v>-2.399839760573464</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.525183062718874</v>
+        <v>-1.535679906301958</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.017430669767727</v>
+        <v>-1.028271251193893</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.007403937544744</v>
+        <v>-1.01819527995513</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.468816247230471</v>
+        <v>-1.479427272402667</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.9327821374391476</v>
+        <v>-0.943735414642866</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.548690824617829</v>
+        <v>-1.559390052253512</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.8151819486109346</v>
+        <v>-0.8263908374494946</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.9952993090305284</v>
+        <v>-1.006477979218296</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.8024491119941644</v>
+        <v>-0.8137144202543425</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.064095257956133</v>
+        <v>-1.075338577568729</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.6556238459960326</v>
+        <v>-0.6463118166211927</v>
       </c>
     </row>
     <row r="21">
@@ -4688,49 +4688,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2561</v>
+        <v>2562</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.017136843908496</v>
+        <v>-1.024605350922705</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.4711215328633074</v>
+        <v>-0.4790485105445654</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.972664465587314</v>
+        <v>-1.980072109208258</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.433026962628126</v>
+        <v>-1.440629702245424</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.705714091885298</v>
+        <v>-0.7136854868998412</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.6207274540410452</v>
+        <v>-0.6286922928947263</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.8012595049073781</v>
+        <v>-0.8091718730268553</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.6631082402697572</v>
+        <v>-0.6711497448609336</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.897724877948427</v>
+        <v>-0.9056892862117465</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.5960661257799345</v>
+        <v>-0.6042812564458941</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.6231760870530607</v>
+        <v>-0.6314167372839847</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.2549438363759648</v>
+        <v>-0.2633281604882924</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.6923767941973793</v>
+        <v>-0.7006591781834643</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.03032750528090133</v>
+        <v>-0.02373302892291207</v>
       </c>
     </row>
     <row r="22">
@@ -4740,49 +4740,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2855</v>
+        <v>2856</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.7500631458724598</v>
+        <v>-0.7555761908689647</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.111290272902167</v>
+        <v>-0.1172067261086411</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.568966473685684</v>
+        <v>-1.574421467892812</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.071198187791587</v>
+        <v>-1.076815845574352</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.7530207892745935</v>
+        <v>-0.7588122634102916</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.8907325267482591</v>
+        <v>-0.8964465697897097</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.747052591240049</v>
+        <v>-0.7528296090005355</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.3565120166169464</v>
+        <v>-0.3624805572462222</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.4333139965461257</v>
+        <v>-0.4392659775459933</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.4248207101538952</v>
+        <v>-0.4308732147603749</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.08526023871863231</v>
+        <v>-0.09145776909284109</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.4238142529136013</v>
+        <v>0.4174387482846313</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.151668707684081</v>
+        <v>-0.1578930621172248</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.2929782305613884</v>
+        <v>0.2977070225074954</v>
       </c>
     </row>
     <row r="23">
@@ -4792,49 +4792,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3052</v>
+        <v>3053</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.5195394621349365</v>
+        <v>-0.5239688681077368</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.2211999227303636</v>
+        <v>-0.2258704759635961</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.218783676009799</v>
+        <v>-1.223165936551652</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.9078378272155732</v>
+        <v>-0.9123127460903575</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.6447360793083377</v>
+        <v>-0.6493468009435048</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.7870773727551281</v>
+        <v>-0.7916181188690459</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.7561446861660954</v>
+        <v>-0.7607056200406532</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.3227593485788489</v>
+        <v>-0.3275056895784729</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.136837493003874</v>
+        <v>-0.1416527129417702</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.1835966157628945</v>
+        <v>-0.1884741352661052</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.1864094878593008</v>
+        <v>0.1813900761428258</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.5339769319709262</v>
+        <v>0.528843951928117</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.1650744324150537</v>
+        <v>0.1600223097482854</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.4661815275295282</v>
+        <v>0.4698754640734393</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3245</v>
+        <v>3246</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.3448809230337986</v>
+        <v>-0.3483600317617217</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.03685104892492319</v>
+        <v>-0.04053674606595337</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.7222393621295495</v>
+        <v>-0.7257436342359327</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.5447427145365964</v>
+        <v>-0.548294556411058</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.5749202649521479</v>
+        <v>-0.5785016659404363</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.5681844051776821</v>
+        <v>-0.5717495059267534</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.6055496038831336</v>
+        <v>-0.6091110135537292</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.2563411875622208</v>
+        <v>-0.2600439982894471</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.2696776329097617</v>
+        <v>-0.2733825685639886</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.08719160028491757</v>
+        <v>-0.09101307490023913</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.03317405857838196</v>
+        <v>0.02929938049583569</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.300483479045063</v>
+        <v>0.2965267460232326</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.07154423645381058</v>
+        <v>-0.07541742617035396</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.2572503560730937</v>
+        <v>0.2601689018988154</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3392</v>
+        <v>3393</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.6872709193289239</v>
+        <v>-0.6899588960657681</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.3447299120226504</v>
+        <v>-0.3476087315276999</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.9295015624860739</v>
+        <v>-0.9322319102333623</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.69531827729854</v>
+        <v>-0.6981117793989995</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.68870147142691</v>
+        <v>-0.6915281588952382</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.4635479609904181</v>
+        <v>-0.4664259876079981</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.4735105518068181</v>
+        <v>-0.4763918945504528</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.1301519170539009</v>
+        <v>-0.1331616615049072</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.2632647346511163</v>
+        <v>-0.2662402920624842</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.06658183397465223</v>
+        <v>-0.06966392066912874</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.1075628262928774</v>
+        <v>-0.110645826890611</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.1790804487513782</v>
+        <v>0.1759132677844448</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.04070709321099031</v>
+        <v>0.03755572033957577</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.3071456957829497</v>
+        <v>0.3094712330546656</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3507</v>
+        <v>3508</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.6752565020281551</v>
+        <v>-0.6774511057970685</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.5102406913441655</v>
+        <v>-0.5125566690527279</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.003575921180719</v>
+        <v>-1.005770922391292</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.715945391724027</v>
+        <v>-0.7182174381019877</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.6987199395278694</v>
+        <v>-0.7010226491656368</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.6419012368669144</v>
+        <v>-0.6442078017635779</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.5120735695211991</v>
+        <v>-0.5144221849027275</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.1383280565656406</v>
+        <v>-0.1408056118247529</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.1551866569153617</v>
+        <v>-0.1576635049602757</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.1066879920060018</v>
+        <v>-0.1092187871833943</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.09606611376523944</v>
+        <v>-0.09861062472101878</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.0683205591636451</v>
+        <v>0.06572944626041988</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.05081878960966435</v>
+        <v>-0.05339652922560134</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.1865311297667347</v>
+        <v>0.188472906968471</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3618</v>
+        <v>3619</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.5518244397362722</v>
+        <v>-0.55360325520396</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.496196506176986</v>
+        <v>-0.4980508980404892</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.7385138720662212</v>
+        <v>-0.7403170345240184</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.4004985104709249</v>
+        <v>-0.4023909935882273</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.3174780026325124</v>
+        <v>-0.3194142133401527</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.3359239384084063</v>
+        <v>-0.3378451123776571</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.350512915585206</v>
+        <v>-0.3524342033658812</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.2232303023396156</v>
+        <v>-0.225204960243893</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.2138632844097899</v>
+        <v>-0.215843811598063</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.0003432976805370913</v>
+        <v>-0.001728801348789943</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.05962587291266885</v>
+        <v>0.05752876900582038</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.1371963308572646</v>
+        <v>0.1350779994532161</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.119368140323985</v>
+        <v>0.1172380977556884</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.2465863332663858</v>
+        <v>0.2481320667998759</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3717</v>
+        <v>3718</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.2682372478239117</v>
+        <v>-0.2697125998187246</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.1495278891946157</v>
+        <v>-0.1510833568421504</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.4226274208866982</v>
+        <v>-0.4241221004690701</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.2242022321431989</v>
+        <v>-0.22574707721121</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.1308077131104284</v>
+        <v>-0.1323943171092736</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.113962489217819</v>
+        <v>-0.1155456380912767</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.1572094599016722</v>
+        <v>-0.1587843146057324</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.1799829389834926</v>
+        <v>-0.1815663069604341</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.01559496660249238</v>
+        <v>0.01395644561813469</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.1746713722097155</v>
+        <v>0.1729641085825833</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.3076192092749324</v>
+        <v>0.3058692948407327</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.3841067015236561</v>
+        <v>0.3823363757705778</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.3018370625637701</v>
+        <v>0.3000755206356516</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.4592705580932943</v>
+        <v>0.460440216914904</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3788</v>
+        <v>3789</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.1124859392575885</v>
+        <v>-0.1137408595716991</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.1576435121216022</v>
+        <v>-0.1589266434613705</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.3803755068410979</v>
+        <v>-0.3816103504584873</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.1832136051096143</v>
+        <v>-0.184497798826456</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.1279591778583509</v>
+        <v>-0.1292717777868333</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.05317791202246269</v>
+        <v>-0.05450357745380074</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.07083457293835949</v>
+        <v>-0.07215833600585597</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.003527759942990372</v>
+        <v>0.002172260236775969</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.1152581800250019</v>
+        <v>0.1138710513027021</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.1499797201992763</v>
+        <v>0.148561850569763</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.2765963849853676</v>
+        <v>0.2751393857944535</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.3786721541200038</v>
+        <v>0.3771883596713224</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.369244328947822</v>
+        <v>0.3677519536428022</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.5020262520579735</v>
+        <v>0.5029672738764503</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3843</v>
+        <v>3844</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.1334798139859075</v>
+        <v>-0.1345328311565979</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.1491105064556848</v>
+        <v>-0.1501934099052349</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.2964556267972824</v>
+        <v>-0.2975090466152182</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.1521346444589327</v>
+        <v>-0.1532233517913184</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.02746720613995279</v>
+        <v>-0.0285999993554924</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.02738164819160005</v>
+        <v>-0.02850885188070862</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.1239119303635405</v>
+        <v>-0.1250163923890639</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.005340216499824635</v>
+        <v>-0.00648574842123395</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.1818816186494914</v>
+        <v>0.1806856043162881</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.1779756707947939</v>
+        <v>0.1767623928752258</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.2478587543405979</v>
+        <v>0.246622452768662</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.3229509522713272</v>
+        <v>0.3216952404477382</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.3336450848464594</v>
+        <v>0.3323772251292496</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.5461553629553109</v>
+        <v>0.54692221326642</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3891</v>
+        <v>3892</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.08565143496407757</v>
+        <v>-0.08654983335125621</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.1977611004814364</v>
+        <v>-0.1986595006473664</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.3737914547374999</v>
+        <v>-0.374652140174895</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.229663395397111</v>
+        <v>-0.2305591797315358</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.1388179530047182</v>
+        <v>-0.1397469411879015</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.0581574385336765</v>
+        <v>-0.05910234976393269</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.1288961713662573</v>
+        <v>-0.1298249015054793</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.00812018462013242</v>
+        <v>0.007147616674423318</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.2179546526691425</v>
+        <v>0.2169266843004607</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.1522817085756003</v>
+        <v>0.1512551291749418</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.2187728451415225</v>
+        <v>0.2177250874675849</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.2419813749866293</v>
+        <v>0.2409277570519492</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.2473398165889336</v>
+        <v>0.2462769023532587</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.4345866213829055</v>
+        <v>0.4352440517076701</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3925</v>
+        <v>3926</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.1064398438260241</v>
+        <v>-0.1072171221819787</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.1553040337584335</v>
+        <v>-0.1560939976459181</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.2824009649740802</v>
+        <v>-0.2831651009364009</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.08754364439330686</v>
+        <v>-0.08835568183802422</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.002100577853184404</v>
+        <v>-0.002943000452667377</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.05504284680485227</v>
+        <v>0.05419005178470826</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.03507658874705299</v>
+        <v>0.03422715093196871</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.1160311744709119</v>
+        <v>0.1151535481926373</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.2726594193509655</v>
+        <v>0.2717405843535161</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.1747602926600393</v>
+        <v>0.173852847980946</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.2134510643873782</v>
+        <v>0.2125301821341239</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.1858255263827999</v>
+        <v>0.1849117650354017</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.2893686344050721</v>
+        <v>0.2884215887311754</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.4007342067792194</v>
+        <v>0.4013042433622189</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3956</v>
+        <v>3957</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.01170488609558618</v>
+        <v>-0.0124021766300686</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.1483587073677839</v>
+        <v>-0.1490434186347187</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.2523384164282518</v>
+        <v>-0.2530025406112841</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.05797849052186876</v>
+        <v>-0.05869020998795094</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.02259440512894884</v>
+        <v>0.02185482041479503</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.005942155944353544</v>
+        <v>0.005210386679955548</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.01069028296691243</v>
+        <v>0.009955823144082387</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.08734990053694247</v>
+        <v>0.08658948318542059</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.1917753801211433</v>
+        <v>0.1909874206491295</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.1132197150848455</v>
+        <v>0.1124398216099678</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.225765423019574</v>
+        <v>0.2249539875077886</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.223893948661896</v>
+        <v>0.2230830615579649</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.2980714613175621</v>
+        <v>0.297235808525393</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.4358014753964241</v>
+        <v>0.4362764760660198</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3980</v>
+        <v>3981</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.07355391620374974</v>
+        <v>0.07291471558482954</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.04689570070930671</v>
+        <v>-0.04752411207802254</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.1776556335067312</v>
+        <v>-0.1782562738842799</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.01633740511738324</v>
+        <v>0.01568939519505363</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.04306684557599283</v>
+        <v>0.0424054405354326</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.05338519140795484</v>
+        <v>0.05272440457974881</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.05760657621139842</v>
+        <v>0.05694340546723708</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.08082783048509867</v>
+        <v>0.08015297027166213</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.2093494880245146</v>
+        <v>0.2086413345370346</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.1261502250033075</v>
+        <v>0.1254525172240761</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.2367872595099243</v>
+        <v>0.2360590136730565</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.2602500726955412</v>
+        <v>0.2595160020856397</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.2560980161870745</v>
+        <v>0.2553596447170108</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.369367180565348</v>
+        <v>0.369793128992292</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4006</v>
+        <v>4007</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.007183725074916936</v>
+        <v>0.006646158520375423</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.04826728409508263</v>
+        <v>-0.04880777176937556</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.1309486009358736</v>
+        <v>-0.1314728114891111</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.01284261235858963</v>
+        <v>0.01228367407009046</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.06081802745318043</v>
+        <v>0.06024136500797539</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.09791339485236961</v>
+        <v>0.09733025872348122</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.1015695405702104</v>
+        <v>0.1009843474261487</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.09669843242738807</v>
+        <v>0.09610938881134246</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.2738584121969723</v>
+        <v>0.2732243041430209</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.1607649933034452</v>
+        <v>0.1601500725979861</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.2444213506932869</v>
+        <v>0.2437831771599264</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.2679569091482037</v>
+        <v>0.2673129204804567</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.2860631607058934</v>
+        <v>0.2854100411616898</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.3752628596597773</v>
+        <v>0.3756168987115345</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/on_chain/hash_rate_ma_ratio_90.xlsx
+++ b/workspaces/btc_daily_14days/on_chain/hash_rate_ma_ratio_90.xlsx
@@ -568,833 +568,833 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.01204</t>
+          <t>X ≈ -0.01203</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>13</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-21.64122399141183</v>
+        <v>-21.67051425303071</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-23.25233387006845</v>
+        <v>-23.25371195083107</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-31.32301665503208</v>
+        <v>-31.32340953095301</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-31.20095168404661</v>
+        <v>-31.20166248709745</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-31.74578267963633</v>
+        <v>-31.69755009590693</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-31.457187529805</v>
+        <v>-31.43345506054111</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-31.54966101890409</v>
+        <v>-31.50189045407075</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-24.34313614014182</v>
+        <v>-24.29406790674327</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-24.41019365519065</v>
+        <v>-24.3371174900465</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-9.89630116281797</v>
+        <v>-9.797085409018237</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-10.10336429259401</v>
+        <v>-10.00355586147572</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-10.07154350218827</v>
+        <v>-9.947925840551669</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-10.4941601147645</v>
+        <v>-10.34551694653957</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-2.57882820697241</v>
+        <v>-2.406829447402245</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.01073</t>
+          <t>X ≈ -0.01071</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>22</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2.058055050899021</v>
+        <v>2.028975771691464</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-4.078868961292564</v>
+        <v>-4.080090933856908</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-9.006431476499117</v>
+        <v>-9.006658346616426</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.1892452192997638</v>
+        <v>0.1887483179183391</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>8.722598638569046</v>
+        <v>8.771079389850001</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>9.021284522198222</v>
+        <v>9.045238184319054</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>8.938915773610056</v>
+        <v>8.986879587167515</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>8.474748703402028</v>
+        <v>8.523951168875087</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>8.415889641287407</v>
+        <v>8.489077444397935</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>12.10959880538215</v>
+        <v>12.20887430024864</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>16.4500749675617</v>
+        <v>16.54993768223984</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>11.94538807730445</v>
+        <v>12.06903552096407</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>20.6169123001456</v>
+        <v>20.76557662109112</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>20.84774521960659</v>
+        <v>21.01974397917325</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.00941</t>
+          <t>X ≈ -0.0094</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>28</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-6.032243454580538</v>
+        <v>-6.061394962863808</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-7.639296824691485</v>
+        <v>-7.640549744340149</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.9117963711022483</v>
+        <v>-0.9119624610567172</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.7823118089318442</v>
+        <v>-0.7828155902277274</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2.24363811127234</v>
+        <v>2.292077675866175</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-1.023497779777571</v>
+        <v>-0.9996001024511969</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2.456721824948062</v>
+        <v>2.504653626580378</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-1.575053194874762</v>
+        <v>-1.52589332462194</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-15.90405679738743</v>
+        <v>-15.83095515522883</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-13.18956995276004</v>
+        <v>-13.09036623453994</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-13.39750670096092</v>
+        <v>-13.29770722435092</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-20.50576276270716</v>
+        <v>-20.3821614794594</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-13.79001287058927</v>
+        <v>-13.64137294626182</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-17.13926776740847</v>
+        <v>-16.96726900784343</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.00809</t>
+          <t>X ≈ -0.008082</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>52</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>7.111081773297435</v>
+        <v>7.082053326923585</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-5.99551523529253</v>
+        <v>-5.996756665801961</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-12.14371275675274</v>
+        <v>-12.14396853363995</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-6.262676428577016</v>
+        <v>-6.263220151794783</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2.791733227748573</v>
+        <v>2.840174428675667</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.7492819407527449</v>
+        <v>-0.7253840524149595</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.8341420161403121</v>
+        <v>-0.7862282769632074</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-3.2208088966145</v>
+        <v>-3.171658126077659</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2.479342190458119</v>
+        <v>2.552505936301444</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1.630641551656119</v>
+        <v>1.729884429865542</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.4951524546488102</v>
+        <v>-0.3953277897199641</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>1.461187162386366</v>
+        <v>1.584817681368541</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>1.041414433935991</v>
+        <v>1.190063872340708</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.6557512838919806</v>
+        <v>-0.4837525243253182</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.006772</t>
+          <t>X ≈ -0.006764</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.1551647105392675</v>
+        <v>-0.7975338153042983</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>18.42257825327714</v>
+        <v>16.83254351736677</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1.690135671099419</v>
+        <v>2.436917062559189</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>2.822938944535814</v>
+        <v>2.570947888225838</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-1.349936513405204</v>
+        <v>-1.424586451919708</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-6.492398571405772</v>
+        <v>-6.401254623423604</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>4.312097677392238</v>
+        <v>3.255052587551319</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.6023736003043183</v>
+        <v>-2.464108007721066</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.6634891611974183</v>
+        <v>-2.501729519215687</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.3033142739067856</v>
+        <v>-1.573066413523321</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.09880441410968643</v>
+        <v>-1.77750194909337</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-3.501276605414084</v>
+        <v>-5.226772425262183</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-3.922331773783348</v>
+        <v>-5.623285408010105</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-5.515891144031848</v>
+        <v>-7.130176276013032</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.005454</t>
+          <t>X ≈ -0.005448</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-10.22143891522423</v>
+        <v>-9.570739789776013</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-8.289601093510548</v>
+        <v>-8.825896213721535</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-9.881814018246551</v>
+        <v>-9.228712766712711</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-8.561109227515288</v>
+        <v>-7.92509079784584</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-9.106362724481954</v>
+        <v>-8.420544875095352</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-11.18612624565807</v>
+        <v>-10.4970530284638</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-10.08407877472225</v>
+        <v>-9.382058332248697</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-10.55774128438527</v>
+        <v>-10.37701453879519</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-10.62263673097291</v>
+        <v>-10.41676166119502</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-15.05145243562016</v>
+        <v>-14.76845639899974</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-8.12370425592588</v>
+        <v>-7.92321127526322</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-9.796548386803124</v>
+        <v>-10.21884813895617</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-7.838995852950291</v>
+        <v>-8.264423516436338</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-8.805934434075141</v>
+        <v>-9.194159764143798</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.004136</t>
+          <t>X ≈ -0.00413</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>123</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-5.311143884257937</v>
+        <v>-4.957246765692354</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.3794939025303989</v>
+        <v>0.7472114019015237</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.8247760322783222</v>
+        <v>-0.4619872733336123</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.738466904971496</v>
+        <v>1.737954560374867</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.232949273786865</v>
+        <v>-1.184535094998196</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-2.559727496017814</v>
+        <v>-2.535843839786317</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-4.2692650842123</v>
+        <v>-4.220057432900859</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.135883675311824</v>
+        <v>0.1852194148155206</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.07487115667544231</v>
+        <v>0.1482132024334177</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.399254033012831</v>
+        <v>-2.29918738193966</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>3.083188219785967</v>
+        <v>3.182303612264917</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.305108586905128</v>
+        <v>2.428755362126445</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.2599436732264166</v>
+        <v>0.4085995654467212</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-4.392461727919496</v>
+        <v>-5.033471098434141</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.002818</t>
+          <t>X ≈ -0.002812</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-2.18346451795486</v>
+        <v>-2.195827159005901</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.569774025252698</v>
+        <v>-2.551856759978669</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.736800303219312</v>
+        <v>-1.720473335165913</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-4.685182165908046</v>
+        <v>-4.651847302416861</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-7.692367699617556</v>
+        <v>-7.590630243041012</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-4.314702716674603</v>
+        <v>-4.258210374675357</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-5.017111633067785</v>
+        <v>-4.931447849470871</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-6.10323576068788</v>
+        <v>-6.008821376931131</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-8.016931612093551</v>
+        <v>-7.885456661954969</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.087850920862891</v>
+        <v>-1.970111590395732</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.942639225960257</v>
+        <v>-2.175120128255834</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.291205952747411</v>
+        <v>-1.504418304319167</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-4.797307736145598</v>
+        <v>-4.966675543029709</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-2.721278349419045</v>
+        <v>-2.878750164721602</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.0015</t>
+          <t>X ≈ -0.001495</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-3.017158075840435</v>
+        <v>-3.230271393771062</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.6767841028042909</v>
+        <v>-0.918497469669326</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.4075434667247464</v>
+        <v>0.1490178074912549</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-4.924631771949265</v>
+        <v>-5.074416930984455</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.987154369825582</v>
+        <v>0.7638345256783197</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2.062156395227909</v>
+        <v>1.522967658441381</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.005090101416585</v>
+        <v>-1.459262434399335</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.008774543140447</v>
+        <v>0.510514402702313</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.043454893295085</v>
+        <v>-1.474596855558524</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>2.86022564290235</v>
+        <v>2.08632062878543</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.661476649679066</v>
+        <v>0.9077383275708542</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.2945275905328089</v>
+        <v>-0.9838746024822598</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-3.205490681927259</v>
+        <v>-3.817661207384937</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.7035890182968814</v>
+        <v>-1.618836952092671</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.0001822</t>
+          <t>X ≈ -0.0001781</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.489883820504254</v>
+        <v>-2.530282703903836</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.466925527662504</v>
+        <v>-1.498367710790326</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-4.505614132041607</v>
+        <v>-4.086350599268869</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.615220474649362</v>
+        <v>-2.206155172729495</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.7082230370289508</v>
+        <v>-0.7020040380053132</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.8513051250043233</v>
+        <v>-0.8667803921532169</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.816989943947597</v>
+        <v>-1.803524313575224</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-4.044733033093884</v>
+        <v>-3.584240967694804</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-4.988020058382908</v>
+        <v>-4.499656630962441</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-4.957070688165956</v>
+        <v>-4.450040090592047</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-8.684872203851455</v>
+        <v>-8.162071228279594</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-4.246545652322055</v>
+        <v>-3.910770381043626</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-5.108867483084872</v>
+        <v>-4.745692011814263</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.799431392329801</v>
+        <v>-1.428421890047417</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ 0.001136</t>
+          <t>X ≈ 0.001139</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>302</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.65269960747478</v>
+        <v>-2.856176091597476</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-3.606717357237471</v>
+        <v>-3.78624767969734</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.172783206329576</v>
+        <v>-1.541344122084688</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.934240724257997</v>
+        <v>1.233854147742306</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>3.049984043948342</v>
+        <v>2.39697503338477</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.693145363291379</v>
+        <v>1.348880363124039</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.3764854560541977</v>
+        <v>-0.6974450749345635</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.174006320499132</v>
+        <v>-1.497303359176989</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.2427358073722203</v>
+        <v>-0.5448965987690713</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.231461182199034</v>
+        <v>-0.1886763664010331</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.29719968640309</v>
+        <v>-1.717851993173014</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.6007996585337807</v>
+        <v>-0.9977719646087166</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.021578630501608</v>
+        <v>-1.065383854134936</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.789220463718777</v>
+        <v>-1.617221704152193</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ 0.002453</t>
+          <t>X ≈ 0.002456</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.806271230815227</v>
+        <v>-1.313739152867754</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.06680972216135928</v>
+        <v>0.573753067954307</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.414053952479073</v>
+        <v>1.76317887479243</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.598649549558992</v>
+        <v>-1.238254319697589</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.438163632426104</v>
+        <v>-1.031490567528429</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.7898408972748072</v>
+        <v>-0.5646522308744224</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-2.626738542320894</v>
+        <v>-2.36480617519711</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.6511039039882576</v>
+        <v>-0.3937477116235897</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-2.962426907241401</v>
+        <v>-2.868340781940013</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-3.113555629096595</v>
+        <v>-2.995754119029236</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-3.669056042865854</v>
+        <v>-3.549776585163265</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-3.634550234304122</v>
+        <v>-3.491624714560935</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.056312108943615</v>
+        <v>-1.449763347209007</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.5680249398843102</v>
+        <v>0.1930097378029529</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 0.003771</t>
+          <t>X ≈ 0.003773</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.654745146985036</v>
+        <v>-1.516531578023816</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.929293673734151</v>
+        <v>-1.914754406721023</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-3.333238868397196</v>
+        <v>-3.3095353324412</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.8241055128319985</v>
+        <v>0.8281447465627991</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.056329119430018</v>
+        <v>-0.9971496659908183</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.5842843895989773</v>
+        <v>0.6112280884089429</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.693564678682861</v>
+        <v>1.553483710175215</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3.575489323486728</v>
+        <v>3.426211525867039</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>4.856789046158582</v>
+        <v>4.727085315209806</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>3.000158840432753</v>
+        <v>2.900918570856838</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.7820348633806091</v>
+        <v>0.6917506828151758</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.8164130157358613</v>
+        <v>0.7498985107618168</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.738544041617082</v>
+        <v>1.69195177753884</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.9575682824476388</v>
+        <v>0.9376521579488539</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 0.005089</t>
+          <t>X ≈ 0.005091</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>305</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>4.388735180906842</v>
+        <v>4.506683150165124</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>2.301340499352712</v>
+        <v>2.260874524008351</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.06064400015650051</v>
+        <v>-0.4320016731735166</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.053187700808913</v>
+        <v>1.011994236356351</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.826373557549353</v>
+        <v>1.505262412876924</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.4844033248893567</v>
+        <v>0.4700692309084502</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.711168375459259</v>
+        <v>1.716276721101806</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>4.522788256262693</v>
+        <v>4.525966319530497</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2.494592984985665</v>
+        <v>2.519795105258389</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>3.939756155868992</v>
+        <v>3.98952776414049</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>6.030136964821985</v>
+        <v>6.266669701308452</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>6.72025282209534</v>
+        <v>6.980726286910318</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>5.316495411404738</v>
+        <v>5.465184959182565</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>6.197968766549451</v>
+        <v>6.369967526116113</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.006407</t>
+          <t>X ≈ 0.006409</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>321</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.347744405602711</v>
+        <v>2.318254116771477</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>5.720981988551344</v>
+        <v>5.717230655200076</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.9648398872854074</v>
+        <v>0.965893550192618</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.7740938476308656</v>
+        <v>-0.7727244564801765</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.491354917030456</v>
+        <v>1.539895660565648</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>2.100255426416204</v>
+        <v>2.123791798570181</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3.884703945654678</v>
+        <v>3.931425641912213</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.236949943612558</v>
+        <v>1.28615697722244</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>3.668179625096151</v>
+        <v>3.741436734875847</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.9491019502615075</v>
+        <v>1.048449275556081</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.990506711004365</v>
+        <v>2.09041474702304</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>3.582517262113697</v>
+        <v>3.706213883141942</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.916260489797203</v>
+        <v>2.064950037575031</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>4.322681498279046</v>
+        <v>4.494680257845708</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.007725</t>
+          <t>X ≈ 0.007726</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>294</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.600716622526832</v>
+        <v>1.386881897389372</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>3.050755019258958</v>
+        <v>3.202395877933839</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.97571152566038</v>
+        <v>1.779351464629251</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2.105936669248663</v>
+        <v>2.251596125696771</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.153441319221137</v>
+        <v>-0.9565168851980772</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-3.237019670538388</v>
+        <v>-3.06312655152972</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.2605055400086016</v>
+        <v>-0.0634479771317018</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>2.3336503060005</v>
+        <v>2.531498839194569</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>3.633212367164802</v>
+        <v>3.706469476944498</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.08261329872613</v>
+        <v>1.181960624020704</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>4.619408739105396</v>
+        <v>4.719316775124071</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>6.354467163569524</v>
+        <v>6.478163784597768</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>4.573772092569079</v>
+        <v>4.722461640346907</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>3.098827470686771</v>
+        <v>3.270826230253434</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>197</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.849033208044439</v>
+        <v>2.819837413691808</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.807838164207318</v>
+        <v>-1.809024950651974</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>3.888761009413273</v>
+        <v>3.888607619408951</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.480915087011844</v>
+        <v>1.480420594633841</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.9426255339161003</v>
+        <v>0.9911714536818721</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.7323853503531552</v>
+        <v>0.7563427593027683</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.8751676485068032</v>
+        <v>-0.8271559695164825</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.180606347300305</v>
+        <v>0.2298539096940218</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>4.18053789636123</v>
+        <v>4.253795006140926</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>3.330619100031484</v>
+        <v>3.429966425326057</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>4.141146368167178</v>
+        <v>4.241054404185853</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.145067667730565</v>
+        <v>2.26876428875881</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>4.770602093605021</v>
+        <v>4.919291641382848</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.965880891039625</v>
+        <v>3.137879650606287</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>193</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.441363762211665</v>
+        <v>2.412167967859034</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2.902716529251563</v>
+        <v>2.901529742806908</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>7.17115757972968</v>
+        <v>7.171004189725359</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>5.228843863214415</v>
+        <v>5.228349370836412</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.5454765899114662</v>
+        <v>0.594022509677238</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.915389479650244</v>
+        <v>2.939346888599857</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.794409690332145</v>
+        <v>1.842421369322466</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.8092063315195901</v>
+        <v>0.8584538939133068</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.360584115158609</v>
+        <v>-2.287327005378913</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.452709523744574</v>
+        <v>1.552056849039147</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.378934639696872</v>
+        <v>-2.279026603678197</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-3.380825917393338</v>
+        <v>-3.257129296365093</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-3.800976770706804</v>
+        <v>-3.652287222928976</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-3.05710640545427</v>
+        <v>-2.885107645887608</v>
       </c>
     </row>
     <row r="24">
@@ -1511,150 +1511,150 @@
         <v>147</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-8.263228955704385</v>
+        <v>-8.292424750057016</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-7.1533266133941</v>
+        <v>-7.154513399838756</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-5.507281671618529</v>
+        <v>-5.50743506162285</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-4.016512310343089</v>
+        <v>-4.017006802721092</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-3.194257645751705</v>
+        <v>-3.145711725985933</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.865021145788177</v>
+        <v>1.88897855473779</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.460582895365505</v>
+        <v>2.508594574355826</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.67378636042227</v>
+        <v>2.723033922815986</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.1082842314746273</v>
+        <v>-0.03502712169493094</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.4023411898825628</v>
+        <v>0.5016885151771362</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-3.203720512595325</v>
+        <v>-3.10381247657665</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.48907025139642</v>
+        <v>-2.365373630368175</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>2.532955766038469</v>
+        <v>2.681645313816297</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1.398147198577924</v>
+        <v>1.570145958144586</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.013</t>
+          <t>X ≈ 0.01299</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>115</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.3070029870560944</v>
+        <v>-0.3361987814087257</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-5.396449949685135</v>
+        <v>-5.39763673612979</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-3.18252568226626</v>
+        <v>-3.182679072270581</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.313170103895288</v>
+        <v>-1.313664596273291</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.9818944395996851</v>
+        <v>-0.9333485198339133</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-5.901911714312469</v>
+        <v>-5.877954305362856</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.638795986622121</v>
+        <v>-1.5907843076318</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.3667341956262007</v>
+        <v>-0.3174866332324839</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.050544517416242</v>
+        <v>3.123801627195938</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.277635148478787</v>
+        <v>-1.178287823184213</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.2567941280435804</v>
+        <v>0.3567021640622556</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-3.187088589166308</v>
+        <v>-3.063391968138063</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.737674225088419</v>
+        <v>-2.588984677310592</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-3.381503792253241</v>
+        <v>-3.209505032686579</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.01432</t>
+          <t>X ≈ 0.01431</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>111</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.374939825321498</v>
+        <v>3.345744030968866</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.03804806954412498</v>
+        <v>-0.03923485598878074</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>7.675288653808941</v>
+        <v>7.67513526380462</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>9.607315599199104</v>
+        <v>9.606821106821101</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>11.7717287488061</v>
+        <v>11.82027466857188</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>9.366400075738497</v>
+        <v>9.39035748468811</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>4.777185211967875</v>
+        <v>4.825196890958196</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.897090639026125</v>
+        <v>-2.847843076632408</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.057171894647936</v>
+        <v>-1.98391478486824</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>3.399215615328451</v>
+        <v>3.498562940623025</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>4.996316258870053</v>
+        <v>5.096224294888728</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>2.327991708522681</v>
+        <v>2.451688329550926</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>5.511444458812932</v>
+        <v>5.660134006590759</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2.133576505435805</v>
+        <v>2.305575265002467</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>99</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>10.14534659572828</v>
+        <v>10.11615080137565</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>12.57456454306848</v>
+        <v>12.57337775662382</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>11.16969214821244</v>
+        <v>11.16953875820812</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>6.249412241295751</v>
+        <v>6.248917748917748</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>6.721223698301038</v>
+        <v>6.76976961806681</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>8.028698738037129</v>
+        <v>8.052656146986742</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>6.933887368669957</v>
+        <v>6.981899047660278</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.416313674378188</v>
+        <v>1.465561236771904</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>8.426038588562463</v>
+        <v>8.499295698342159</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>6.566018782131621</v>
+        <v>6.665366107426195</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>9.39162065417446</v>
+        <v>9.491528690193135</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>9.425998806529812</v>
+        <v>9.549695427558056</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>6.985645933014325</v>
+        <v>7.134335480792153</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>8.221482593341896</v>
+        <v>8.393481352908559</v>
       </c>
     </row>
     <row r="28">
@@ -1719,150 +1719,150 @@
         <v>71</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>8.082464251155784</v>
+        <v>8.053268456803153</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.570975363034762</v>
+        <v>-0.5721621494794178</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.851154660660868</v>
+        <v>1.851001270656546</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.981379804249229</v>
+        <v>1.980885311871226</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.03463954692821858</v>
+        <v>0.08318546669399041</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>3.148914985014017</v>
+        <v>3.17287239396363</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>4.4726553299732</v>
+        <v>4.520667008963521</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>9.639389503087834</v>
+        <v>9.688637065481551</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>5.353055233888952</v>
+        <v>5.426312343668648</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.130666379342273</v>
+        <v>-1.0313190540477</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.335367537602465</v>
+        <v>-1.23545950158379</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.1074613189781317</v>
+        <v>0.2311579400063764</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>3.912662578340814</v>
+        <v>4.061352126118642</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>2.729947524341988</v>
+        <v>2.90194628390865</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.01827</t>
+          <t>X ≈ 0.01826</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-1.571825121443496</v>
+        <v>-0.6582599730351362</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.4533524218563585</v>
+        <v>1.46226664551272</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.513126491646837</v>
+        <v>6.624084212753615</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2.006987998871502</v>
+        <v>3.050264550264487</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>6.923243900321317</v>
+        <v>8.116570964868181</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.766072475410894</v>
+        <v>2.833800928131552</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-3.773183338400678</v>
+        <v>-2.782410716649409</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.6038883458238757</v>
+        <v>0.4554602266709011</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>4.789674952198801</v>
+        <v>5.974043173089662</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>2.121574337687171</v>
+        <v>3.298362740422817</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.719490456936704</v>
+        <v>-0.6094814108169686</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-3.503294122763101</v>
+        <v>-2.403166525303881</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-2.10526315789479</v>
+        <v>-0.9464726000159587</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>3.575017946877303</v>
+        <v>4.858127817555065</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.01959</t>
+          <t>X ≈ 0.01958</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>48</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>3.769083969465704</v>
+        <v>1.65655484177968</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-4.092102123598245</v>
+        <v>-6.176622243376229</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-6.570206841686613</v>
+        <v>-8.653693565024263</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-6.439981698098187</v>
+        <v>-8.523809523809469</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-9.061604584527274</v>
+        <v>-11.09639199809478</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-2.51423055489213</v>
+        <v>-4.573606479275853</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.5156075808249909</v>
+        <v>-2.550929235168013</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1.100657108721684</v>
+        <v>-0.9334286622179917</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>3.123008285532208</v>
+        <v>1.112932061978583</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.893577177464344</v>
+        <v>-3.877563185503099</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-2.098278335724473</v>
+        <v>-4.08170363303919</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-6.230566850035878</v>
+        <v>-8.190203562340962</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-6.650717703349201</v>
+        <v>-8.585361488904738</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-8.508315386456118</v>
+        <v>-10.41964996022273</v>
       </c>
     </row>
     <row r="31">
@@ -1872,205 +1872,205 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-2.480916030534353</v>
+        <v>-1.08154039631556</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.731427288166529</v>
+        <v>5.906711089957163</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>10.21900884458795</v>
+        <v>11.22725881592817</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>16.23158692935279</v>
+        <v>17.07142857142857</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>15.6932973762571</v>
+        <v>16.58217943047665</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>13.04949493530395</v>
+        <v>13.99782209215272</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>18.84713751721421</v>
+        <v>19.65145171721294</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>12.49771593225105</v>
+        <v>13.47133324254391</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>6.554380834551836</v>
+        <v>7.720074919121359</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>2.763285567633702</v>
+        <v>4.039103481163565</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.38259206121473</v>
+        <v>0.9778201764846131</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-6.230566850035878</v>
+        <v>-4.67829880043621</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>5.113988179003613</v>
+        <v>6.355114701571395</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-3.483805582534472</v>
+        <v>-1.967269007841843</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.02222</t>
+          <t>X ≈ 0.02221</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>31</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>12.03521300172371</v>
+        <v>12.00601720737108</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.7466075538211712</v>
+        <v>0.7454207673765154</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>3.577642620679043</v>
+        <v>3.577489230674722</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3.707867764267405</v>
+        <v>3.707373271889402</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>3.169578211171753</v>
+        <v>3.218124130937525</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-6.210467114031871</v>
+        <v>-6.186509705082258</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-3.069371021685143</v>
+        <v>-3.021359342694822</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-3.536439665471924</v>
+        <v>-3.487192103078208</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-10.04903472522051</v>
+        <v>-9.975777615440812</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-7.673147069937457</v>
+        <v>-7.573799744642884</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>1.799571126641062</v>
+        <v>1.899479162659738</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>5.05975573060924</v>
+        <v>5.183452351637484</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>1.413798425682977</v>
+        <v>1.562487973460804</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>4.865340527522406</v>
+        <v>5.037339287089068</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.02354</t>
+          <t>X ≈ 0.02353</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>24</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>14.18575063613229</v>
+        <v>14.15655484177966</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>16.74123120973518</v>
+        <v>16.74004442329052</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>12.17979315831344</v>
+        <v>12.17963976830912</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>12.3100183019018</v>
+        <v>12.3095238095238</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>3.438395415472719</v>
+        <v>3.486941335238491</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>7.902436111774499</v>
+        <v>7.926393520724112</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>7.817725752508309</v>
+        <v>7.86573743149863</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.9826762246117084</v>
+        <v>-0.9334286622179917</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>3.123008285532187</v>
+        <v>3.196265395311883</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>2.273089489202292</v>
+        <v>2.372436814496865</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>2.068388330942135</v>
+        <v>2.16829636696081</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>6.269433149964158</v>
+        <v>6.393129770992402</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-6.650717703349287</v>
+        <v>-6.502028155571459</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-10.59164871978945</v>
+        <v>-10.41964996022279</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.02486</t>
+          <t>X ≈ 0.02485</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>26</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-10.17322372284202</v>
+        <v>-10.20241951719465</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.2459482774443629</v>
+        <v>-0.2471350638890186</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>7.05158803010832</v>
+        <v>7.051434640103999</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.5104945186109831</v>
+        <v>-0.5109890109889861</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>2.797369774447112</v>
+        <v>2.845915694212884</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>6.940897650236046</v>
+        <v>6.964855059185659</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>6.856187290969906</v>
+        <v>6.904198969960227</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>2.542964801029314</v>
+        <v>2.59221236342303</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>10.17429033681424</v>
+        <v>10.24754744659393</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>5.478217694330553</v>
+        <v>5.577565019625126</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>1.427362689916485</v>
+        <v>1.527270725935161</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>1.461740842271844</v>
+        <v>1.585437463300089</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>4.887743835112254</v>
+        <v>5.036433382890081</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>1.267325639184968</v>
+        <v>1.43932439875163</v>
       </c>
     </row>
   </sheetData>
@@ -2210,833 +2210,833 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.0127</t>
+          <t>X &gt; -0.01269</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4007</v>
+        <v>4018</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.006646158520375423</v>
+        <v>0.007873786623804335</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.224892153585202</v>
+        <v>0.2243289559621289</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.2418472482420952</v>
+        <v>0.2411935037273381</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.2612256705849063</v>
+        <v>0.2605334089941778</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.3092453490717162</v>
+        <v>0.3063271476713041</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.2218632599687993</v>
+        <v>0.2202335604658288</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.2255483733354708</v>
+        <v>0.222880288641548</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.2705424812608754</v>
+        <v>0.2676979116720091</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.2732243041430209</v>
+        <v>0.2693451865124743</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.1850815111419948</v>
+        <v>0.1803267531675488</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.1939078654392219</v>
+        <v>0.1891037946321958</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.2673129204804567</v>
+        <v>0.2612889749724587</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.3353102407624888</v>
+        <v>0.3280290725947523</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.3756168987115345</v>
+        <v>0.367225765677361</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.01138</t>
+          <t>X &gt; -0.01137</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3994</v>
+        <v>4005</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.0771074284124964</v>
+        <v>0.07824058924940402</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.3013077615740585</v>
+        <v>0.3005373284435962</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.3445871658040858</v>
+        <v>0.3436503924791054</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.3636313555148618</v>
+        <v>0.3626578900551465</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.4135806931811743</v>
+        <v>0.4102098952784132</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.3249748424092189</v>
+        <v>0.3229796159147824</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.3289729407113171</v>
+        <v>0.3258570725754524</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.3506571087216344</v>
+        <v>0.347423992980211</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.3535659249420391</v>
+        <v>0.3492163512553574</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.2178952254037654</v>
+        <v>0.2127128600610462</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.2274242745665234</v>
+        <v>0.2221885825296752</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.3009646814956568</v>
+        <v>0.2944274999666661</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.3705588923954011</v>
+        <v>0.3626747900101677</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.3852332698617289</v>
+        <v>0.3762301895899753</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.01007</t>
+          <t>X &gt; -0.01006</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3972</v>
+        <v>3983</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.06613541237656761</v>
+        <v>0.06746575269058752</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.3255685591327406</v>
+        <v>0.3247336181173637</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.3963803204190626</v>
+        <v>0.3952965868703018</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.3645972404586431</v>
+        <v>0.3636184751887157</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.3675589422248535</v>
+        <v>0.3640288435885921</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.2768079710710154</v>
+        <v>0.2748024407943035</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.2812844355945643</v>
+        <v>0.2780181332530773</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.3056596225476724</v>
+        <v>0.3022611514362268</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.3089105569260298</v>
+        <v>0.3042560338942906</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.1520297977200968</v>
+        <v>0.1464523650361542</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.1375707208792392</v>
+        <v>0.1320026723630576</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.2364688822238108</v>
+        <v>0.2293907496623859</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.2584189691903518</v>
+        <v>0.2499798765570489</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.2718960939064488</v>
+        <v>0.2622062620552512</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.008749</t>
+          <t>X &gt; -0.00874</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3944</v>
+        <v>3955</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.1094301913509099</v>
+        <v>0.1108559170485037</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.3821142565838258</v>
+        <v>0.3811250047542316</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.4056675788781305</v>
+        <v>0.4045515181830552</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.3727395967930605</v>
+        <v>0.3717348225544939</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.3542399217549317</v>
+        <v>0.3503789403512343</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.2860393506409338</v>
+        <v>0.2838247596845349</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.2658401539257227</v>
+        <v>0.2622543421498733</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.3190115391013819</v>
+        <v>0.3152038379923994</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.4240127592386074</v>
+        <v>0.4184876175341046</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.2467470373279568</v>
+        <v>0.2401643551216424</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.2336615342188821</v>
+        <v>0.2270802645521854</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.3837261048551568</v>
+        <v>0.3753132433198871</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.3581542865113008</v>
+        <v>0.3483257372495672</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.395504762293065</v>
+        <v>0.3841848480368313</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.007431</t>
+          <t>X &gt; -0.007423</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3892</v>
+        <v>3903</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.01588294513785371</v>
+        <v>0.01797806275346403</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.4673241059100235</v>
+        <v>0.4660980631372453</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.5733365864456559</v>
+        <v>0.5717365150302953</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.4613936649634809</v>
+        <v>0.4601328903654505</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.3216732074919264</v>
+        <v>0.3172071839093036</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.2998720092104321</v>
+        <v>0.2972705342756683</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.2805367296820052</v>
+        <v>0.2762233650025223</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.3663061595169097</v>
+        <v>0.3616595956484687</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.396552037135983</v>
+        <v>0.3900559104944179</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.2282571825630413</v>
+        <v>0.220316688227804</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.243399028417528</v>
+        <v>0.2353726598435486</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.3693304278274994</v>
+        <v>0.3591989131178508</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.3490254253432425</v>
+        <v>0.3371111886908338</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.4095503209779636</v>
+        <v>0.3957484512555922</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.006113</t>
+          <t>X &gt; -0.006106</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3837</v>
+        <v>3846</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.01388646426813978</v>
+        <v>0.03006443224106192</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.2099514246212024</v>
+        <v>0.2235376390886117</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.5573282597175009</v>
+        <v>0.5440934335926713</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.4275430028898555</v>
+        <v>0.4288493607559758</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.3456342537909407</v>
+        <v>0.3430215981688463</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.3972331981428994</v>
+        <v>0.3965466481573188</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.2227478706452359</v>
+        <v>0.2320753500037469</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.3801913267804338</v>
+        <v>0.4035391467124398</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.4117467897834501</v>
+        <v>0.4329138848816925</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.2271813055695873</v>
+        <v>0.2468956889557745</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.2454716642754633</v>
+        <v>0.2652046548277909</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.4248121549133259</v>
+        <v>0.4419863198489153</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.4102515514709282</v>
+        <v>0.4254477997183841</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.4944862815136801</v>
+        <v>0.507287117260347</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.004795</t>
+          <t>X &gt; -0.004789</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3753</v>
+        <v>3761</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.242974482354299</v>
+        <v>0.2470461814756888</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.4001892107984091</v>
+        <v>0.4280582127362678</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.7909781268501845</v>
+        <v>0.7649624915628763</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.6287278649612773</v>
+        <v>0.6176515180229671</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.5571897417139127</v>
+        <v>0.5410814626270906</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.6564930418091137</v>
+        <v>0.6427460558980229</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.4534362368085283</v>
+        <v>0.4493583500014751</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.6250051661990099</v>
+        <v>0.6471836729735827</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.6587194025581766</v>
+        <v>0.6781205909217221</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.5691491271149971</v>
+        <v>0.586248235479637</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.4327913491400892</v>
+        <v>0.4502659029154614</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.6535876106831608</v>
+        <v>0.6829251470221251</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.5948869849831553</v>
+        <v>0.6218421261935632</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.7026491752278972</v>
+        <v>0.7265434280605021</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.003477</t>
+          <t>X &gt; -0.003471</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3630</v>
+        <v>3638</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.4311718815535599</v>
+        <v>0.4230022102007283</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.400890456781049</v>
+        <v>0.4172677118381642</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.8457268214983458</v>
+        <v>0.806445400051679</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.5911251371592741</v>
+        <v>0.5797743123579622</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.6178473447184913</v>
+        <v>0.5994241884621445</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.7654724154049006</v>
+        <v>0.7502134987702576</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.6134616534712265</v>
+        <v>0.6072302964822214</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.6415787043199828</v>
+        <v>0.6628025854951503</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.6785026902285765</v>
+        <v>0.6960366461124963</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.6697313829540406</v>
+        <v>0.6838041950570357</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.3429845130272966</v>
+        <v>0.3578962937208487</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.5976269825632414</v>
+        <v>0.6238990017615933</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.6062363038112792</v>
+        <v>0.6290518114524559</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.8752934289709131</v>
+        <v>0.9212882842339027</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.002159</t>
+          <t>X &gt; -0.002154</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3468</v>
+        <v>3475</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.5533088759942615</v>
+        <v>0.5458422640656693</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.5396585208206872</v>
+        <v>0.5565388741133077</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.9663639017187222</v>
+        <v>0.9249742500777103</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.8375962395516865</v>
+        <v>0.8251712398999231</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.006040781045606</v>
+        <v>0.9835907704290534</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.00278163437747</v>
+        <v>0.9851410070786457</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.876481512877028</v>
+        <v>0.8670301634722577</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.9566478921317696</v>
+        <v>0.9757449468981605</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.084690797776496</v>
+        <v>1.098564245886593</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.7985457812292225</v>
+        <v>0.8082900290221531</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.4497524039488496</v>
+        <v>0.4767111647373099</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.6858596629324225</v>
+        <v>0.7237308638885409</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.8586509907988784</v>
+        <v>0.8915276557058718</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.043299377096396</v>
+        <v>1.099534692055414</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.0008412</t>
+          <t>X &gt; -0.0008367</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3267</v>
+        <v>3270</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.7729794781732551</v>
+        <v>0.7825711019422883</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.6144993433944848</v>
+        <v>0.6490105715064161</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.000744956947919</v>
+        <v>0.9736198374569796</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.192113481765254</v>
+        <v>1.195023097707654</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.007202754922325</v>
+        <v>0.9973675380663352</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.9376043074931886</v>
+        <v>0.9514240457546776</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.9922439537931638</v>
+        <v>1.012868078629339</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.9534408346316923</v>
+        <v>1.004910776121449</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1.215623544610111</v>
+        <v>1.259878626864044</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.6717023002998346</v>
+        <v>0.7281688446333234</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.3752018764337706</v>
+        <v>0.4496895841927042</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.7461773360106321</v>
+        <v>0.830782582728304</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.10869460151757</v>
+        <v>1.186752033973029</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.150775522634824</v>
+        <v>1.269952486260415</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; 0.0004767</t>
+          <t>X &gt; 0.0004805</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3040</v>
+        <v>3042</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.016620915278452</v>
+        <v>1.030871781670399</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.7699215294898636</v>
+        <v>0.8099580561755957</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.411910586290219</v>
+        <v>1.352868114765826</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.476411116010688</v>
+        <v>1.449943757030368</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.135295404518679</v>
+        <v>1.124736610829103</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.071184057880345</v>
+        <v>1.087699723546592</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.202012406025787</v>
+        <v>1.22395863268018</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.326659738570413</v>
+        <v>1.348870867373954</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.67885614259675</v>
+        <v>1.69155977044867</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.092008704372773</v>
+        <v>1.116279179028922</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.051727144928755</v>
+        <v>1.09514700209003</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.118989217047321</v>
+        <v>1.186165250624427</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.572966507177028</v>
+        <v>1.631392810580365</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.371070578456191</v>
+        <v>1.472197508547787</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 0.001795</t>
+          <t>X &gt; 0.001798</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2738</v>
+        <v>2740</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.42134509273334</v>
+        <v>1.459298226096266</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.252662560823559</v>
+        <v>1.316547155530934</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.697000990005044</v>
+        <v>1.671865229922339</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.425912744319412</v>
+        <v>1.4737609329446</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.9241062266122668</v>
+        <v>0.9845117919926807</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.002582043916085</v>
+        <v>1.058912660352291</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.37611991309231</v>
+        <v>1.435733785855234</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.602481926239875</v>
+        <v>1.662573282125194</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.890806752125833</v>
+        <v>1.938059706033982</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.186926656051547</v>
+        <v>1.260110045714988</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.310812573366377</v>
+        <v>1.405192876750419</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.308681050657803</v>
+        <v>1.426876578726763</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.859143509214633</v>
+        <v>1.92862877873511</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.719649064481338</v>
+        <v>1.812710137100851</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 0.003112</t>
+          <t>X &gt; 0.003115</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2452</v>
+        <v>2453</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.797812575822611</v>
+        <v>1.783742468967311</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.390979816882854</v>
+        <v>1.403453760966933</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.730003784757258</v>
+        <v>1.661181570697828</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.778696111386793</v>
+        <v>1.791065611912508</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.199640149811685</v>
+        <v>1.220383246204889</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.211649320090878</v>
+        <v>1.24886909075672</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.843011233748172</v>
+        <v>1.880395411954716</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.865339001054416</v>
+        <v>1.903162000105574</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.456885392655622</v>
+        <v>2.500406603730077</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.688532664841254</v>
+        <v>1.758044418027104</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.891661849158552</v>
+        <v>1.984922283831224</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.885256967256133</v>
+        <v>2.002339224945096</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>2.199200730582191</v>
+        <v>2.32389928022144</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.853973901200241</v>
+        <v>2.002214423525025</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 0.00443</t>
+          <t>X &gt; 0.004432</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2154</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>2.275464479906489</v>
+        <v>2.241858504273885</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.850330559781582</v>
+        <v>1.864059258710057</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2.430489537143529</v>
+        <v>2.351174307020294</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.910761105987234</v>
+        <v>1.924730114577123</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.511747318908256</v>
+        <v>1.528202345901505</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.298443539815388</v>
+        <v>1.337381003338884</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.863686755293884</v>
+        <v>1.925774520047597</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.628744388201667</v>
+        <v>1.691745190355036</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2.124865295745742</v>
+        <v>2.191317961793018</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.507072776110405</v>
+        <v>1.599400327174692</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2.045175703272683</v>
+        <v>2.16442939093605</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.033128600289103</v>
+        <v>2.176192416003964</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.262931321720352</v>
+        <v>2.411620869498179</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.977989163218936</v>
+        <v>2.149987922785598</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 0.005748</t>
+          <t>X &gt; 0.00575</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1849</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.926871962975653</v>
+        <v>1.868266553491395</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.775934653037837</v>
+        <v>1.798602981849051</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2.841412051408817</v>
+        <v>2.810270398939757</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.052221294510424</v>
+        <v>2.075289575289574</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.459848453150805</v>
+        <v>1.531986380283598</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.432722753202327</v>
+        <v>1.480447574778204</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.888845276575424</v>
+        <v>1.960332026093283</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.151360191469053</v>
+        <v>1.224228995439667</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2.063877223696963</v>
+        <v>2.137134333476659</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.105791850839246</v>
+        <v>1.205139176133819</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.387840286954386</v>
+        <v>1.487748322973061</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.259968574517934</v>
+        <v>1.383665195546179</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.75923362169128</v>
+        <v>1.907923169469107</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.281886524486758</v>
+        <v>1.45388528405342</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.007066</t>
+          <t>X &gt; 0.007067</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1528</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.838455697214336</v>
+        <v>1.773733825865143</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.9471648921086242</v>
+        <v>0.9753834248165418</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3.235639580652013</v>
+        <v>3.19773438352604</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2.645969436282257</v>
+        <v>2.673596187984671</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.453229621406457</v>
+        <v>1.530324810276703</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.292488467795479</v>
+        <v>1.345294763366397</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.469558213241356</v>
+        <v>1.546247568843363</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.133379621810626</v>
+        <v>1.211219255811223</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.726847727067955</v>
+        <v>1.800104836847652</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.138709035450148</v>
+        <v>1.238056360744721</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.261233008080005</v>
+        <v>1.36114104409868</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.7720509510112379</v>
+        <v>0.8957475720394825</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.726245647436052</v>
+        <v>1.87493519521388</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.6430807741023727</v>
+        <v>0.8150795336690351</v>
       </c>
     </row>
     <row r="22">
@@ -3049,98 +3049,98 @@
         <v>1234</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.895096935429997</v>
+        <v>1.865901141077366</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.4459853966611362</v>
+        <v>0.4447986102164805</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>3.535816929248078</v>
+        <v>3.535663539243757</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.774632024214078</v>
+        <v>2.774137531836075</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2.074267916823402</v>
+        <v>2.122813836589174</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.371641946458489</v>
+        <v>2.395599355408102</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.881745201454876</v>
+        <v>1.929756880445197</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.8474156176357255</v>
+        <v>0.8966631800294422</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.272657123997874</v>
+        <v>1.34591423377757</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.152073821995415</v>
+        <v>1.251421147289989</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.4611490008502912</v>
+        <v>0.5610570368689665</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.5579574497117292</v>
+        <v>-0.4342608286834846</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.047823625662055</v>
+        <v>1.196513173439882</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.05800011867626864</v>
+        <v>0.229998878242931</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.009702</t>
+          <t>X &gt; 0.009701</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1037</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.713876640632471</v>
+        <v>1.684680846279839</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.8741466710016255</v>
+        <v>0.8729598845569697</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3.468767764549384</v>
+        <v>3.468614374545062</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>3.020400815563008</v>
+        <v>3.019906323185005</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2.289247231609075</v>
+        <v>2.337793151374846</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.683053276673284</v>
+        <v>2.707010685622897</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2.405478886548863</v>
+        <v>2.453490565539184</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.9740900884709021</v>
+        <v>1.023337650864619</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.7202439010898871</v>
+        <v>0.7935010108695835</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.7382132436221198</v>
+        <v>0.8375605689166932</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.2379440380710491</v>
+        <v>-0.1380360020523739</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.071454024577818</v>
+        <v>-0.9477574035495735</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.3406034152620947</v>
+        <v>0.4892929630399223</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.4944131042317181</v>
+        <v>-0.3224143446650558</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>844</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.547519988422998</v>
+        <v>1.518324194070367</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.4102675446482635</v>
+        <v>0.4090807582036078</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2.622131230983271</v>
+        <v>2.62197784097895</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2.515389549927086</v>
+        <v>2.514895057549083</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2.68800047076504</v>
+        <v>2.736546390530812</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2.629924263433303</v>
+        <v>2.653881672382916</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.545213904167134</v>
+        <v>2.593225583157455</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.011794549479916</v>
+        <v>1.061042111873633</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.424746042246248</v>
+        <v>1.498003152025944</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.5748272459163886</v>
+        <v>0.6741745712109619</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.2516426753339118</v>
+        <v>0.3515507113525871</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.5433630585666833</v>
+        <v>-0.4196664375384387</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>1.28767092224313</v>
+        <v>1.436360470020958</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.09160562460235866</v>
+        <v>0.263604384169021</v>
       </c>
     </row>
     <row r="25">
@@ -3205,98 +3205,98 @@
         <v>697</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.616644945075407</v>
+        <v>3.587449150722776</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.005458852011579</v>
+        <v>2.004272065566923</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>4.33665590341149</v>
+        <v>4.336502513407169</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>3.892992955177753</v>
+        <v>3.89249846279975</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.928591493904158</v>
+        <v>3.977137413669929</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.791245293983998</v>
+        <v>2.815202702933611</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.563062911762316</v>
+        <v>2.611074590752636</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.6612740384203377</v>
+        <v>0.7105216008140545</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1.748068065541752</v>
+        <v>1.821325175321448</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.6112052233008498</v>
+        <v>0.7105525485954232</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.9803921568627487</v>
+        <v>1.080300192881424</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.133005874426118</v>
+        <v>-0.009309253397873363</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.025035524771233</v>
+        <v>1.173725072549061</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.1839490545574805</v>
+        <v>-0.01195029499081812</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.01366</t>
+          <t>X &gt; 0.01365</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>582</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>4.39193620314262</v>
+        <v>4.362740408789989</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>3.468035333446487</v>
+        <v>3.466848547001831</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>5.822404842162243</v>
+        <v>5.822251452157921</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>4.921702150699062</v>
+        <v>4.921207658321059</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>4.898876515129139</v>
+        <v>4.947422434894911</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>4.508965321396531</v>
+        <v>4.532922730346144</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>3.39332712707882</v>
+        <v>3.44133880606914</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.8644028131889812</v>
+        <v>0.9136503755826979</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.4907058800339</v>
+        <v>1.563962989813596</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.9844296953878882</v>
+        <v>1.083777020682462</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>1.123371148811543</v>
+        <v>1.223279184830218</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.4704640777991713</v>
+        <v>0.594160698827416</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1.768526282905015</v>
+        <v>1.917215830682842</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.4478701805542187</v>
+        <v>0.619868940120881</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>471</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>4.631610508743776</v>
+        <v>4.602414714391145</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>4.29430976599842</v>
+        <v>4.293122979553765</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>5.385737956614932</v>
+        <v>5.385584566610611</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>3.817449299778666</v>
+        <v>3.816954807400663</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3.279159746682971</v>
+        <v>3.327705666448743</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>3.364219551264981</v>
+        <v>3.388176960214594</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.067194966945735</v>
+        <v>3.115206645936055</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.750869422946678</v>
+        <v>1.800116985340395</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2.326829941583135</v>
+        <v>2.400087051362831</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.4153400199878874</v>
+        <v>0.5146873452824607</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.2106388617276949</v>
+        <v>0.3105468977463701</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.0327027890299405</v>
+        <v>0.1563994100581851</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.8864372860349974</v>
+        <v>1.035126833812825</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.05060181099614169</v>
+        <v>0.222600570562804</v>
       </c>
     </row>
     <row r="28">
@@ -3361,202 +3361,202 @@
         <v>372</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3.164245259788224</v>
+        <v>3.135049465435593</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>2.090693575326547</v>
+        <v>2.089506788881891</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3.846459824980116</v>
+        <v>3.846306434975794</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>3.170233355665253</v>
+        <v>3.16973886328725</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.363126598268487</v>
+        <v>2.411672518034258</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2.122866219301422</v>
+        <v>2.146823628251035</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2.038155860035253</v>
+        <v>2.086167539025574</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1.839904420549587</v>
+        <v>1.889151982943304</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.7036534468225</v>
+        <v>0.7769105566021963</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.221534166711656</v>
+        <v>-1.122186841417083</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-2.232686937875073</v>
+        <v>-2.132778901856398</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-2.467125989820829</v>
+        <v>-2.343429368792584</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.7367392087256377</v>
+        <v>-0.5880496609478101</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-2.123906784305554</v>
+        <v>-1.951908024738891</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.01761</t>
+          <t>X &gt; 0.0176</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>301</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2.004133803352694</v>
+        <v>1.974938009000063</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>2.718529105637693</v>
+        <v>2.717342319193037</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>4.31711320261023</v>
+        <v>4.316959812605909</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>3.450660605334811</v>
+        <v>3.450166112956808</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2.912371052239116</v>
+        <v>2.960916972004888</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.880841427389157</v>
+        <v>1.90479883633877</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>1.463905154501724</v>
+        <v>1.511916833492045</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.0001587698511897884</v>
+        <v>0.04940633224490654</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.3930493002928372</v>
+        <v>-0.3197921905131409</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.242968096622697</v>
+        <v>-1.143620771328123</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-2.444346995746685</v>
+        <v>-2.344438959728009</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-3.074420670633877</v>
+        <v>-2.950724049605633</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-1.833441955840975</v>
+        <v>-1.684752408063147</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-3.268835873720754</v>
+        <v>-3.096837114154091</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.01893</t>
+          <t>X &gt; 0.01892</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.803636814994107</v>
+        <v>2.550616920052285</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3.224971047133522</v>
+        <v>2.991731332872135</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>4.049711857500434</v>
+        <v>3.812568243342859</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3.773432936048152</v>
+        <v>3.537593984962406</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>2.0156311878305</v>
+        <v>1.833769945225058</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.906501152424944</v>
+        <v>1.701697164448845</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>2.634798923240069</v>
+        <v>2.450757674413659</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.1352099542500866</v>
+        <v>-0.03936658394538739</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.55178846243529</v>
+        <v>-1.695772391462746</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.995203193724507</v>
+        <v>-2.114742672682588</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-2.606408417025342</v>
+        <v>-2.72374141981382</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-2.978534329710676</v>
+        <v>-3.070432982044068</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-1.772668922861477</v>
+        <v>-1.846157710227324</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-4.798965792960153</v>
+        <v>-4.835979244973096</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.02025</t>
+          <t>X &gt; 0.02024</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.569589019970699</v>
+        <v>2.766270084660754</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.998806967310912</v>
+        <v>5.203193502017463</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>6.624237602757894</v>
+        <v>6.81950576495904</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>6.249412241295751</v>
+        <v>6.446877243359651</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>4.701021678099039</v>
+        <v>4.952602976779595</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>2.978193687532112</v>
+        <v>3.215338244342234</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>3.398533833316442</v>
+        <v>3.657194717930842</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.09883784077332081</v>
+        <v>0.1762865806630813</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-2.685072522548616</v>
+        <v>-2.373248842544072</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-2.019839803726967</v>
+        <v>-1.689539734916835</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-2.729591467037665</v>
+        <v>-2.396192745267001</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-2.190162809631836</v>
+        <v>-1.835513445088033</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.5901116427432314</v>
+        <v>-0.2206211203955775</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-3.899729527870221</v>
+        <v>-3.489164198078711</v>
       </c>
     </row>
     <row r="32">
@@ -3569,202 +3569,202 @@
         <v>164</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.616644945075407</v>
+        <v>3.587449150722776</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>5.054239339816448</v>
+        <v>5.053052553371792</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>5.878980150183367</v>
+        <v>5.878826760179045</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.179937001088796</v>
+        <v>4.179442508710792</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>2.422135252871151</v>
+        <v>2.470681172636922</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.8902409898233188</v>
+        <v>0.9141983987729319</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.1957745329961753</v>
+        <v>0.243786211986496</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-2.710318501034472</v>
+        <v>-2.661070938640755</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-4.600568950240174</v>
+        <v>-4.527311840460477</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-3.011463356326125</v>
+        <v>-2.912116031031552</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-3.216164514586318</v>
+        <v>-3.116256478567642</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-1.352518069548069</v>
+        <v>-1.228821448519824</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-1.772668922861477</v>
+        <v>-1.62397937508365</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-3.985957662878853</v>
+        <v>-3.813958903312191</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.02288</t>
+          <t>X &gt; 0.02287</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>133</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.654422315330308</v>
+        <v>1.625226520977677</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>6.058273816251443</v>
+        <v>6.057087029806787</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>6.415382130744526</v>
+        <v>6.415228740740204</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4.289968176588523</v>
+        <v>4.28947368421052</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>2.247919224996586</v>
+        <v>2.296465144762358</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>2.545293254631673</v>
+        <v>2.569250663581286</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.9568234968692622</v>
+        <v>1.004835175859583</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-2.517763943909955</v>
+        <v>-2.468516381516238</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-3.330625799680845</v>
+        <v>-3.257368689901149</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-1.924905498266348</v>
+        <v>-1.825558172971775</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-4.385245754270898</v>
+        <v>-4.285337718252222</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-2.847108203419332</v>
+        <v>-2.723411582391087</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-2.515379357484626</v>
+        <v>-2.366689809706799</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-6.049042203498693</v>
+        <v>-5.877043443932031</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.0242</t>
+          <t>X &gt; 0.02419</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>109</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-1.104769241543522</v>
+        <v>-1.133965035896153</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>3.706063014016493</v>
+        <v>3.704876227571837</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>5.146154014582557</v>
+        <v>5.146000624578235</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>2.524085580189272</v>
+        <v>2.523591087811269</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1.985796027093578</v>
+        <v>2.03434194685935</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.365738864068106</v>
+        <v>1.389696273017719</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.5538338805191572</v>
+        <v>-0.5058222015288365</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-2.855764909626998</v>
+        <v>-2.806517347233282</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-4.751609451470877</v>
+        <v>-4.678352341691181</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-2.849234669819076</v>
+        <v>-2.749887344524502</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-5.806229406060929</v>
+        <v>-5.706321370042254</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-4.854420061045047</v>
+        <v>-4.730723440016803</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-1.604846143716259</v>
+        <v>-1.456156595938431</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-5.048835264131924</v>
+        <v>-4.876836504565262</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.02552</t>
+          <t>X &gt; 0.02551</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>83</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1.735951439345165</v>
+        <v>1.706755644992533</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>4.944042454715074</v>
+        <v>4.942855668270418</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>4.549271069960035</v>
+        <v>4.549117679955714</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>3.474676936439955</v>
+        <v>3.474182444061952</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>1.731568106235841</v>
+        <v>1.780114026001613</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.3806964183459485</v>
+        <v>-0.3567390093963354</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-2.875045331828986</v>
+        <v>-2.827033652838665</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-4.546933252724159</v>
+        <v>-4.497685690330442</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-9.427192517680666</v>
+        <v>-9.35393540790097</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-5.457834205576795</v>
+        <v>-5.358486880282221</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-8.072173918053849</v>
+        <v>-7.972265882035174</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-6.832976488590099</v>
+        <v>-6.709279867561854</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-3.638669510578197</v>
+        <v>-3.489979962800369</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-7.027391691676975</v>
+        <v>-6.855392932110313</v>
       </c>
     </row>
   </sheetData>
@@ -3904,833 +3904,833 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.0127</t>
+          <t>X &lt; -0.01269</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>83</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1.735951439345165</v>
+        <v>1.706755644992533</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-8.308969593477698</v>
+        <v>-8.310156379922354</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-13.52301808666648</v>
+        <v>-13.5231714766708</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-8.573515834644375</v>
+        <v>-8.574010327022378</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-10.3166246648485</v>
+        <v>-10.26807874508273</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-6.404792803888114</v>
+        <v>-6.380835394938501</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-8.899141717371151</v>
+        <v>-8.85113003838083</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-12.98066819248319</v>
+        <v>-12.93142063008947</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-9.427192517680666</v>
+        <v>-9.35393540790097</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-6.662653482685229</v>
+        <v>-6.563306157390656</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-5.662535363836987</v>
+        <v>-5.562627327818312</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-6.832976488590099</v>
+        <v>-6.709279867561854</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-6.048308064795073</v>
+        <v>-5.899618517017245</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-7.027391691676975</v>
+        <v>-6.855392932110313</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.01138</t>
+          <t>X &lt; -0.01137</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>96</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-1.439249363867688</v>
+        <v>-1.46844515822032</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-10.34210212359818</v>
+        <v>-10.34328891004284</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-15.94520684168655</v>
+        <v>-15.94536023169087</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-11.64831503143153</v>
+        <v>-11.64880952380953</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-13.22827125119388</v>
+        <v>-13.17972533142811</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-9.805897221558794</v>
+        <v>-9.781939812609181</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-11.97394091415831</v>
+        <v>-11.92592923516798</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-14.52434289127837</v>
+        <v>-14.47509532888466</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-11.46032504780115</v>
+        <v>-11.38706793802145</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-7.10191051079768</v>
+        <v>-7.002563185503107</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-6.264945002391201</v>
+        <v>-6.165036966372526</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-7.272233516702549</v>
+        <v>-7.148536895674305</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-6.650717703349287</v>
+        <v>-6.502028155571459</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-6.424982053122754</v>
+        <v>-6.252983293556092</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.01007</t>
+          <t>X &lt; -0.01006</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>118</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.7860007762970653</v>
+        <v>-0.8151965706496966</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-9.176847886310043</v>
+        <v>-9.178034672754698</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-14.65636503377695</v>
+        <v>-14.65651842378127</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-9.44139412747672</v>
+        <v>-9.441888619854723</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-9.13222605345377</v>
+        <v>-9.083680133687999</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-6.292479142462753</v>
+        <v>-6.26852173351314</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-8.072104755966215</v>
+        <v>-8.024093076975895</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-10.23408865399023</v>
+        <v>-10.18484109159652</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-7.75269792915708</v>
+        <v>-7.679440819377383</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-3.517870962775071</v>
+        <v>-3.418523637480497</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-2.027656866797983</v>
+        <v>-1.927748830779308</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-3.68819396867994</v>
+        <v>-3.564497347651695</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-1.565971940637425</v>
+        <v>-1.417282392859597</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-1.340236290410893</v>
+        <v>-1.16823753084423</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.008749</t>
+          <t>X &lt; -0.00874</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>146</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-1.795984523685036</v>
+        <v>-1.825180318037667</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-8.886622671543392</v>
+        <v>-8.887809457988048</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-12.02112008369568</v>
+        <v>-12.02127347370001</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-7.781305899011436</v>
+        <v>-7.781800391389439</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-6.949732438408503</v>
+        <v>-6.901186518642731</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-5.282495395074783</v>
+        <v>-5.25853798612517</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-6.052137261190261</v>
+        <v>-6.00412558219994</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-8.57400042552495</v>
+        <v>-8.524752863131233</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-9.319914088897036</v>
+        <v>-9.24665697911734</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-5.375312337281692</v>
+        <v>-5.275965011987118</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-4.210150481843257</v>
+        <v>-4.110242445824582</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-6.915498356885195</v>
+        <v>-6.79180173585695</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-3.910991675952026</v>
+        <v>-3.762302128174198</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-4.370187532574811</v>
+        <v>-4.198188773008148</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.007431</t>
+          <t>X &lt; -0.007423</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>198</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.5493869997686787</v>
+        <v>0.5201912054160474</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-8.132506164002223</v>
+        <v>-8.133692950446878</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-12.0626310841108</v>
+        <v>-12.06278447411512</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-7.386951395067889</v>
+        <v>-7.387445887445892</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-4.389887412810047</v>
+        <v>-4.341341493044276</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-4.09251338317496</v>
+        <v>-4.068555974225347</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-4.682274247491634</v>
+        <v>-4.634262568501313</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-7.169544911480394</v>
+        <v>-7.120297349086677</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-6.220426057902159</v>
+        <v>-6.147168948122463</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-3.534991318878475</v>
+        <v>-3.435643993583902</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-3.23464197208817</v>
+        <v>-3.134733936069495</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-4.715415334884362</v>
+        <v>-4.591718713856118</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-2.610313662945245</v>
+        <v>-2.461624115167417</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-3.394679022819723</v>
+        <v>-3.222680263253061</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.006113</t>
+          <t>X &lt; -0.006106</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.4602604400538866</v>
+        <v>0.2242631751130162</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-2.327396241245232</v>
+        <v>-2.530788910042837</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-8.996677429921846</v>
+        <v>-8.783901898357541</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-5.144049939568006</v>
+        <v>-5.138392857142861</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-3.713835555655827</v>
+        <v>-3.674516998094781</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-4.597563888225466</v>
+        <v>-4.573606479275853</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-2.713770310483767</v>
+        <v>-2.869556686148364</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-5.742228266772443</v>
+        <v>-6.080487485747405</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-5.012696589303125</v>
+        <v>-5.333146369394001</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.700560049664603</v>
+        <v>-3.019720048248196</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-2.510004290928748</v>
+        <v>-2.83170363303919</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-4.451910723553667</v>
+        <v>-4.734321209399795</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-2.895776991886834</v>
+        <v>-3.168694822238123</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-3.855812092648449</v>
+        <v>-4.096120548458046</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.004795</t>
+          <t>X &lt; -0.004789</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-2.186798383475526</v>
+        <v>-2.217714164068276</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-3.797984476539355</v>
+        <v>-4.093288910042837</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-9.192755861294394</v>
+        <v>-8.872991810638247</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-5.979067243820907</v>
+        <v>-5.819131161236434</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-5.042430543229287</v>
+        <v>-4.846391998094781</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-6.219982767281515</v>
+        <v>-6.035594783369426</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-4.534781622122907</v>
+        <v>-4.487635002518907</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-6.924490820272453</v>
+        <v>-7.158918858296417</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-6.393757000463872</v>
+        <v>-6.607656173315569</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-5.76438585596533</v>
+        <v>-5.960896518836435</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-3.898081097065756</v>
+        <v>-4.106213436960758</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-5.785462992469114</v>
+        <v>-6.106870229007633</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-4.128462510470946</v>
+        <v>-4.443204626159691</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-5.089670480422463</v>
+        <v>-5.370630352379628</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.003477</t>
+          <t>X &lt; -0.003471</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-3.020872833990076</v>
+        <v>-2.939296374243206</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.6882144346133</v>
+        <v>-2.805735261974164</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-6.970674804249548</v>
+        <v>-6.632949645138659</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-3.923747931864426</v>
+        <v>-3.819508448540709</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-4.029137052059681</v>
+        <v>-3.878650062610916</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-5.246914537576117</v>
+        <v>-5.111240887878004</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-4.465824031041421</v>
+        <v>-4.418745327121997</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-5.040883021430218</v>
+        <v>-5.208086689575801</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-4.668025698560363</v>
+        <v>-4.813093855948019</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-4.86718527580129</v>
+        <v>-4.988974272616133</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.035010078313107</v>
+        <v>-2.169356620800173</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-3.621871197861971</v>
+        <v>-3.839051654493595</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.95506552943624</v>
+        <v>-3.154295974145967</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-4.903242922687973</v>
+        <v>-5.28106104733579</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.002159</t>
+          <t>X &lt; -0.002154</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-2.800404848425728</v>
+        <v>-2.748585592772514</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-2.654402443086994</v>
+        <v>-2.74193755869149</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-5.605084370973024</v>
+        <v>-5.361430713937828</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-4.116648364764863</v>
+        <v>-4.038671519563245</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-4.974937917860558</v>
+        <v>-4.846391998094781</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-4.997563888225464</v>
+        <v>-4.892077816855469</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-4.602274247491629</v>
+        <v>-4.554517751914389</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-5.309599301534782</v>
+        <v>-5.419584146776032</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-5.530837868313967</v>
+        <v>-5.616301164858513</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-4.137166921054082</v>
+        <v>-4.203708020433886</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.011333445408859</v>
+        <v>-2.171426742730354</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-3.01513276643459</v>
+        <v>-3.231470867985266</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-3.435283619747999</v>
+        <v>-3.626628794549092</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-4.334949898781915</v>
+        <v>-4.655539204099227</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.0008412</t>
+          <t>X &lt; -0.0008367</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>823</v>
+        <v>831</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.842361813666884</v>
+        <v>-2.869824055102811</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.164391280224685</v>
+        <v>-2.294727758963703</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-4.125427725220689</v>
+        <v>-4.007410591403108</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-4.296334733884279</v>
+        <v>-4.297118847539018</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-3.507724407607235</v>
+        <v>-3.465839777206426</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-3.269061472766531</v>
+        <v>-3.313102277595185</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-3.716090672612403</v>
+        <v>-3.79291641465516</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-3.758774572052261</v>
+        <v>-3.956894366189111</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-4.424351649977687</v>
+        <v>-4.595551692534094</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.4282825850511</v>
+        <v>-2.651630574191437</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.113429850876052</v>
+        <v>-1.411727700427875</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.347071704404811</v>
+        <v>-2.677267340920984</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.374018674223066</v>
+        <v>-3.674109984692997</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-3.448068322867591</v>
+        <v>-3.906412896444181</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; 0.0004767</t>
+          <t>X &lt; 0.0004805</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1050</v>
+        <v>1059</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.764469905770653</v>
+        <v>-2.792066712105026</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-2.012707038532021</v>
+        <v>-2.119604699516522</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-4.203319633116919</v>
+        <v>-4.017102086327469</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-3.930915157574695</v>
+        <v>-3.839739282354529</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.906301554224186</v>
+        <v>-2.868990868151279</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-2.749222655997976</v>
+        <v>-2.784529266469832</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-3.307866664553245</v>
+        <v>-3.361878025617237</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-3.821069646496589</v>
+        <v>-3.873680234545027</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-4.546188425410264</v>
+        <v>-4.571030202172395</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.973824091044584</v>
+        <v>-3.03636821694964</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.747834736231503</v>
+        <v>-2.863150173919692</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.757683881434545</v>
+        <v>-2.943508567062402</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-3.748719606298856</v>
+        <v>-3.905238731586572</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-3.091648719789418</v>
+        <v>-3.372907750591025</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 0.001795</t>
+          <t>X &lt; 0.001798</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1352</v>
+        <v>1361</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.73807988064457</v>
+        <v>-2.802509485705698</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-2.365430558572463</v>
+        <v>-2.48510177553991</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-3.530991155412046</v>
+        <v>-3.463635085492051</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-2.627435708399879</v>
+        <v>-2.711202842512286</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.581241305194865</v>
+        <v>-1.698514984917622</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.76042313656739</v>
+        <v>-1.864968119100155</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-2.655745139164445</v>
+        <v>-2.766130700369438</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-3.231938761484862</v>
+        <v>-3.340564537095801</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-3.587906168745107</v>
+        <v>-3.670792278197403</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.259505836750932</v>
+        <v>-2.402569299467395</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.424472328831378</v>
+        <v>-2.606709747003485</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.276390944640461</v>
+        <v>-2.509219715057561</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-3.14000077799821</v>
+        <v>-3.271484836922411</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.80072169809317</v>
+        <v>-2.983328627869099</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 0.003112</t>
+          <t>X &lt; 0.003115</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1638</v>
+        <v>1648</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-2.571880251274195</v>
+        <v>-2.540286839974492</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.939282232755239</v>
+        <v>-1.950862838829806</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.666485158838654</v>
+        <v>-2.554659748599093</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-2.444080058753926</v>
+        <v>-2.453819594302978</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.553504139002712</v>
+        <v>-1.58157942252042</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.588445347192028</v>
+        <v>-1.639547193129459</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.645800083357898</v>
+        <v>-2.697216563658699</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.777080117555741</v>
+        <v>-2.828744632337106</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-3.475693276650816</v>
+        <v>-3.531980112461184</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-2.406163454362428</v>
+        <v>-2.506351064290982</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-2.639107098673961</v>
+        <v>-2.771097572433135</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-2.51105465491392</v>
+        <v>-2.680551247806903</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.776404097492062</v>
+        <v>-2.954423546717607</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-2.212527840668542</v>
+        <v>-2.430167759575511</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 0.00443</t>
+          <t>X &lt; 0.004432</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1936</v>
+        <v>1947</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-2.429581328275624</v>
+        <v>-2.382365274043863</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.936044628731658</v>
+        <v>-1.94604964623916</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.766277719960819</v>
+        <v>-2.671170120863934</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.941437676172875</v>
+        <v>-1.951820441585028</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.47591478161376</v>
+        <v>-1.492577353957557</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.253942489048512</v>
+        <v>-1.294917954685687</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.980267042139083</v>
+        <v>-2.045846371679175</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.802278009712971</v>
+        <v>-1.86932609811543</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.196414692314292</v>
+        <v>-2.265273066226577</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.575707761656787</v>
+        <v>-1.676648186358243</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.113320453654737</v>
+        <v>-2.23994717673682</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.999400699365083</v>
+        <v>-2.154098155085663</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.081796691475262</v>
+        <v>-2.241247868097126</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.724568829982253</v>
+        <v>-1.912973021342438</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 0.005748</t>
+          <t>X &lt; 0.00575</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2241</v>
+        <v>2252</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.504873439584934</v>
+        <v>-1.450041153508899</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.362408381920417</v>
+        <v>-1.37565744738265</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-2.399839760573464</v>
+        <v>-2.365010983238172</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.535679906301958</v>
+        <v>-1.548651039363115</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.028271251193893</v>
+        <v>-1.085330051192123</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.01819527995513</v>
+        <v>-1.054350171174924</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.479427272402667</v>
+        <v>-1.534173994542051</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.943735414642866</v>
+        <v>-1.001734673146949</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.559390052253512</v>
+        <v>-1.614693104171216</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.8263908374494946</v>
+        <v>-0.9077050294747409</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.006477979218296</v>
+        <v>-1.087431644864765</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.8137144202543425</v>
+        <v>-0.916098268049339</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.075338577568729</v>
+        <v>-1.197989096539054</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.6463118166211927</v>
+        <v>-0.7911715706431224</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.007066</t>
+          <t>X &lt; 0.007067</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2562</v>
+        <v>2573</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.024605350922705</v>
+        <v>-0.9820654032235439</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.4790485105445654</v>
+        <v>-0.4942177026125023</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.980072109208258</v>
+        <v>-1.9512158259611</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.440629702245424</v>
+        <v>-1.452417837778029</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.7136854868998412</v>
+        <v>-0.7588290380017995</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.6286922928947263</v>
+        <v>-0.6588777971053119</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.8091718730268553</v>
+        <v>-0.8537274773807297</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.6711497448609336</v>
+        <v>-0.7168525049901575</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.9056892862117465</v>
+        <v>-0.9477739116444184</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.6042812564458941</v>
+        <v>-0.6640397085919716</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.6314167372839847</v>
+        <v>-0.6914344819004725</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.2633281604882924</v>
+        <v>-0.3398799377455006</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.7006591781834643</v>
+        <v>-0.7910724446157502</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.02373302892291207</v>
+        <v>-0.1317240630858265</v>
       </c>
     </row>
     <row r="22">
@@ -4740,101 +4740,101 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2856</v>
+        <v>2867</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.7555761908689647</v>
+        <v>-0.7392784915536481</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.1172067261086411</v>
+        <v>-0.1162135366493047</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.574421467892812</v>
+        <v>-1.568333361178944</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.076815845574352</v>
+        <v>-1.072471324296146</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.7588122634102916</v>
+        <v>-0.7782417894716929</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.8964465697897097</v>
+        <v>-0.9040412618845508</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.7528296090005355</v>
+        <v>-0.7720496248687425</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.3624805572462222</v>
+        <v>-0.3837709293023366</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.4392659775459933</v>
+        <v>-0.471329776461566</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.4308732147603749</v>
+        <v>-0.4750031019085341</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.09145776909284109</v>
+        <v>-0.1371624019125903</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.4174387482846313</v>
+        <v>0.3587972509505377</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.1578930621172248</v>
+        <v>-0.2258775279563991</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.2977070225074954</v>
+        <v>0.2171945927361989</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.009702</t>
+          <t>X &lt; 0.009701</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3053</v>
+        <v>3064</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.5239688681077368</v>
+        <v>-0.511411792387797</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.2258704759635961</v>
+        <v>-0.2246283118633841</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.223165936551652</v>
+        <v>-1.218734215430707</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.9123127460903575</v>
+        <v>-0.9088669950739003</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.6493468009435048</v>
+        <v>-0.6648104816613269</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.7916181188690459</v>
+        <v>-0.7975648126091883</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.7607056200406532</v>
+        <v>-0.7755846134378217</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.3275056895784729</v>
+        <v>-0.3443950031517531</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.1416527129417702</v>
+        <v>-0.1680226463955137</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.1884741352661052</v>
+        <v>-0.224260273725605</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.1813900761428258</v>
+        <v>0.1440598709277765</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.528843951928117</v>
+        <v>0.4815185511619759</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.1600223097482854</v>
+        <v>0.104823394183839</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.4698754640734393</v>
+        <v>0.4049801529191086</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3246</v>
+        <v>3257</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.3483600317617217</v>
+        <v>-0.3388580022570125</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.04053674606595337</v>
+        <v>-0.04006162341083552</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.7257436342359327</v>
+        <v>-0.7232570085166543</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.548294556411058</v>
+        <v>-0.5463072281254142</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.5785016659404363</v>
+        <v>-0.5904213918486079</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.5717495059267534</v>
+        <v>-0.5766692664121464</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.6091110135537292</v>
+        <v>-0.6207821763444485</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.2600439982894471</v>
+        <v>-0.2732488685720611</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.2733825685639886</v>
+        <v>-0.2934137381440749</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.09101307490023913</v>
+        <v>-0.1191301894896029</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.02929938049583569</v>
+        <v>0.0006072054066095234</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.2965267460232326</v>
+        <v>0.2601135083351167</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.07541742617035396</v>
+        <v>-0.1177433182479533</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.2601689018988154</v>
+        <v>0.2100194697230009</v>
       </c>
     </row>
     <row r="25">
@@ -4896,101 +4896,101 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3393</v>
+        <v>3404</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.6899588960657681</v>
+        <v>-0.6810219799938011</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.3476087315276999</v>
+        <v>-0.3462163105112168</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.9322319102333623</v>
+        <v>-0.9291938090456853</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.6981117793989995</v>
+        <v>-0.6957485982090574</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.6915281588952382</v>
+        <v>-0.7004793113089534</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.4664259876079981</v>
+        <v>-0.4704411803309512</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.4763918945504528</v>
+        <v>-0.4859189742474257</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.1331616615049072</v>
+        <v>-0.14408359867938</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.2662402920624842</v>
+        <v>-0.2822718101247119</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.06966392066912874</v>
+        <v>-0.09235191789747432</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.110645826890611</v>
+        <v>-0.1333375240479029</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.1759132677844448</v>
+        <v>0.1467997651203774</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.03755572033957577</v>
+        <v>0.003111345162757573</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.3094712330546656</v>
+        <v>0.2687558368786895</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.01366</t>
+          <t>X &lt; 0.01365</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3508</v>
+        <v>3519</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.6774511057970685</v>
+        <v>-0.6697947240942312</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.5125566690527279</v>
+        <v>-0.510734392908887</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.005770922391292</v>
+        <v>-1.002607634901445</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.7182174381019877</v>
+        <v>-0.7158847103590702</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.7010226491656368</v>
+        <v>-0.708070002629924</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.6442078017635779</v>
+        <v>-0.6467564650995001</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.5144221849027275</v>
+        <v>-0.5219540035552015</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.1408056118247529</v>
+        <v>-0.1497407189555773</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.1576635049602757</v>
+        <v>-0.1711201514153231</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.1092187871833943</v>
+        <v>-0.1277997263300463</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.09861062472101878</v>
+        <v>-0.1173367960147758</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.06572944626041988</v>
+        <v>0.04195112856123728</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.05339652922560134</v>
+        <v>-0.08157361011691222</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.188472906968471</v>
+        <v>0.1550871810105505</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3619</v>
+        <v>3630</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.55360325520396</v>
+        <v>-0.5474436942254428</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.4980508980404892</v>
+        <v>-0.4963641434310873</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.7403170345240184</v>
+        <v>-0.7380568351880896</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.4023909935882273</v>
+        <v>-0.401098901098905</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.3194142133401527</v>
+        <v>-0.3259193407713425</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.3378451123776571</v>
+        <v>-0.3405113720740971</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.3524342033658812</v>
+        <v>-0.358760781314075</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.225204960243893</v>
+        <v>-0.2321085302047905</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.215843811598063</v>
+        <v>-0.2264764662195233</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.001728801348789943</v>
+        <v>-0.01703300755410453</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.05752876900582038</v>
+        <v>0.04195450073454765</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.1350779994532161</v>
+        <v>0.1155967313447874</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.1172380977556884</v>
+        <v>0.09395091355550989</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.2481320667998759</v>
+        <v>0.2208459075458435</v>
       </c>
     </row>
     <row r="28">
@@ -5052,205 +5052,205 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3718</v>
+        <v>3729</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.2697125998187246</v>
+        <v>-0.2653229419366809</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.1510833568421504</v>
+        <v>-0.1504928662042886</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.4241221004690701</v>
+        <v>-0.4228557753628905</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.22574707721121</v>
+        <v>-0.22502196920491</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.1323943171092736</v>
+        <v>-0.1379917840765899</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.1155456380912767</v>
+        <v>-0.118160934721395</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.1587843146057324</v>
+        <v>-0.1642411552250849</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.1815663069604341</v>
+        <v>-0.1871100544535977</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.01395644561813469</v>
+        <v>0.004871001453643942</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.1729641085825833</v>
+        <v>0.1601857206492312</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.3058692948407327</v>
+        <v>0.2926264848600582</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.3823363757705778</v>
+        <v>0.3659252681781098</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.3000755206356516</v>
+        <v>0.2808136674848356</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.460440216914904</v>
+        <v>0.4378185299890944</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.01761</t>
+          <t>X &lt; 0.0176</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3789</v>
+        <v>3800</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.1137408595716991</v>
+        <v>-0.1104265377115254</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.1589266434613705</v>
+        <v>-0.158346622529713</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.3816103504584873</v>
+        <v>-0.3804931801733389</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.184497798826456</v>
+        <v>-0.1839145106861722</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.1292717777868333</v>
+        <v>-0.1338690261861402</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.05450357745380074</v>
+        <v>-0.05679975658678416</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.07215833600585597</v>
+        <v>-0.07686829479498414</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.002172260236775969</v>
+        <v>-0.002880405080141202</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.1138710513027021</v>
+        <v>0.1060332446329468</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.148561850569763</v>
+        <v>0.1379468039816487</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.2751393857944535</v>
+        <v>0.2640979271326032</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.3771883596713224</v>
+        <v>0.3634085716236157</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.3677519536428022</v>
+        <v>0.3514314603190982</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.5029672738764503</v>
+        <v>0.4838588117070728</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.01893</t>
+          <t>X &lt; 0.01892</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3844</v>
+        <v>3854</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.1345328311565979</v>
+        <v>-0.1180766555050354</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.1501934099052349</v>
+        <v>-0.1357100171302648</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.2975090466152182</v>
+        <v>-0.2826284507508134</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.1532233517913184</v>
+        <v>-0.1387163561076648</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.0285999993554924</v>
+        <v>-0.01853799861251559</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.02850885188070862</v>
+        <v>-0.01638224312878123</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.1250163923890639</v>
+        <v>-0.1147080489467882</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.00648574842123395</v>
+        <v>0.003531614120525717</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.1806856043162881</v>
+        <v>0.1881458479334555</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.1767623928752258</v>
+        <v>0.1821827968711887</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.246622452768662</v>
+        <v>0.2518673634174675</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.3216952404477382</v>
+        <v>0.3246650407019089</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.3323772251292496</v>
+        <v>0.3332507030537002</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.54692221326642</v>
+        <v>0.5451485175492508</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.02025</t>
+          <t>X &lt; 0.02024</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3892</v>
+        <v>3902</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.08654983335125621</v>
+        <v>-0.09631872143870623</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.1986595006473664</v>
+        <v>-0.2097937644117707</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.374652140174895</v>
+        <v>-0.3853146571104205</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.2305591797315358</v>
+        <v>-0.241600934852471</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.1397469411879015</v>
+        <v>-0.1544973419965956</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.05910234976393269</v>
+        <v>-0.07232770689734025</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.1298249015054793</v>
+        <v>-0.1446232745642462</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.007147616674423318</v>
+        <v>-0.007976598076062658</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.2169266843004607</v>
+        <v>0.1995074395060641</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.1512551291749418</v>
+        <v>0.1322934453212739</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.2177250874675849</v>
+        <v>0.198599397263834</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.2409277570519492</v>
+        <v>0.2199740332874498</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.2462769023532587</v>
+        <v>0.2235675400472985</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.4352440517076701</v>
+        <v>0.410266322025663</v>
       </c>
     </row>
     <row r="32">
@@ -5260,205 +5260,205 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3926</v>
+        <v>3937</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.1072171221819787</v>
+        <v>-0.1050485337477411</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.1560939976459181</v>
+        <v>-0.1555831617521264</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.2831651009364009</v>
+        <v>-0.2823663107182313</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.08835568183802422</v>
+        <v>-0.0880777443990084</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.002943000452667377</v>
+        <v>-0.006047345281800176</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.05419005178470826</v>
+        <v>0.05250251945671636</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.03422715093196871</v>
+        <v>0.0310518331214098</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.1151535481926373</v>
+        <v>0.1116723606918057</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.2717405843535161</v>
+        <v>0.2662806160120326</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.173852847980946</v>
+        <v>0.1669898044317719</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.2125301821341239</v>
+        <v>0.2055214092619906</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.1849117650354017</v>
+        <v>0.1764504107486502</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.2884215887311754</v>
+        <v>0.2780632613914733</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.4013042433622189</v>
+        <v>0.3891299906704759</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.02288</t>
+          <t>X &lt; 0.02287</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3957</v>
+        <v>3968</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.0124021766300686</v>
+        <v>-0.01073980780584805</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.1490434186347187</v>
+        <v>-0.1485652919523872</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.2530025406112841</v>
+        <v>-0.2522945535472871</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.05869020998795094</v>
+        <v>-0.05850032320621068</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.02185482041479503</v>
+        <v>0.01908449172166371</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.005210386679955548</v>
+        <v>0.003858309456546749</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.009955823144082387</v>
+        <v>0.007246865460949437</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.08658948318542059</v>
+        <v>0.08359868218731492</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.1909874206491295</v>
+        <v>0.1863652359025352</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.1124398216099678</v>
+        <v>0.1065757873065607</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.2249539875077886</v>
+        <v>0.2187454561910656</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.2230830615579649</v>
+        <v>0.2155479070125139</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.297235808525393</v>
+        <v>0.2880953012186609</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.4362764760660198</v>
+        <v>0.425444125798748</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.0242</t>
+          <t>X &lt; 0.02419</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3981</v>
+        <v>3992</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.07291471558482954</v>
+        <v>0.07415783803435971</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.04752411207802254</v>
+        <v>-0.04733486408878917</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.1782562738842799</v>
+        <v>-0.1777588493942659</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.01568939519505363</v>
+        <v>0.01567073606053526</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.0424054405354326</v>
+        <v>0.0398864322976209</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.05272440457974881</v>
+        <v>0.05139352072414738</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.05694340546723708</v>
+        <v>0.05440959954069058</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.08015297027166213</v>
+        <v>0.07749346551254632</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.2086413345370346</v>
+        <v>0.2044381915757398</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.1254525172240761</v>
+        <v>0.1201845622446527</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.2360590136730565</v>
+        <v>0.2304574015874294</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.2595160020856397</v>
+        <v>0.2526690799558153</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.2553596447170108</v>
+        <v>0.2472831391943799</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.369793128992292</v>
+        <v>0.3602431593497144</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.02552</t>
+          <t>X &lt; 0.02551</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4007</v>
+        <v>4018</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.006646158520375423</v>
+        <v>0.007873786623804335</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.04880777176937556</v>
+        <v>-0.04862389763589192</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.1314728114891111</v>
+        <v>-0.1311073153344608</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.01228367407009046</v>
+        <v>0.01227124414809566</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.06024136500797539</v>
+        <v>0.05800333341750985</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.09733025872348122</v>
+        <v>0.09604081332226144</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.1009843474261487</v>
+        <v>0.09865668615707079</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.09610938881134246</v>
+        <v>0.09374164924656014</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.2732243041430209</v>
+        <v>0.2693451865124743</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.1601500725979861</v>
+        <v>0.1554635010541645</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.2437831771599264</v>
+        <v>0.2388426655598295</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.2673129204804567</v>
+        <v>0.2612889749724587</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.2854100411616898</v>
+        <v>0.2782654498030155</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.3756168987115345</v>
+        <v>0.367225765677361</v>
       </c>
     </row>
   </sheetData>
